--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14236" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15247" uniqueCount="1111">
   <si>
     <t>Property</t>
   </si>
@@ -1342,7 +1342,7 @@
     <t>ChargeItem.subject.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-kvid-10}
 </t>
   </si>
   <si>
@@ -1629,7 +1629,7 @@
     <t>ChargeItem.enterer.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-telematik-id}
 </t>
   </si>
   <si>
@@ -2628,21 +2628,6 @@
     <t>Consent.patient.identifier.type</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://fhir.de/CodeSystem/identifier-type-de-basis"/&gt;
-    &lt;code value="KVZ10"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>http://fhir.de/ValueSet/identifier-type-de-basis</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-kvid-2:Die type Codes 'GKV' und 'PKV' haben den Status 'retired', daher sollen diese nicht mehr verwendet werden {($this.coding.exists(system='http://fhir.de/CodeSystem/identifier-type-de-basis' and code='GKV') or $this.coding.exists(system='http://fhir.de/CodeSystem/identifier-type-de-basis' and code='PKV')).not()}</t>
-  </si>
-  <si>
     <t>Consent.patient.identifier.system</t>
   </si>
   <si>
@@ -2652,20 +2637,12 @@
     <t>Consent.patient.identifier.value</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-kvid-1:Der unveränderliche Teil der KVID muss 10-stellig sein und mit einem Großbuchstaben anfangen {matches('^[A-Z][0-9]{9}$')}</t>
-  </si>
-  <si>
     <t>Consent.patient.identifier.period</t>
   </si>
   <si>
     <t>Consent.patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
     <t>Consent.patient.identifier.assigner.id</t>
   </si>
   <si>
@@ -2681,7 +2658,7 @@
     <t>Consent.patient.identifier.assigner.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-iknr}
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-iknr}
 </t>
   </si>
   <si>
@@ -3395,6 +3372,78 @@
   </si>
   <si>
     <t>Parameters.parameter:markingFlag.part:taxOffice.part</t>
+  </si>
+  <si>
+    <t>identifier-iknr</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-iknr</t>
+  </si>
+  <si>
+    <t>IdentifierIknr</t>
+  </si>
+  <si>
+    <t>Identifier IKNR</t>
+  </si>
+  <si>
+    <t>2026-02-25T12:53:52+00:00</t>
+  </si>
+  <si>
+    <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Identifier</t>
+  </si>
+  <si>
+    <t>An identifier intended for computation</t>
+  </si>
+  <si>
+    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+  </si>
+  <si>
+    <t>Identifier.id</t>
+  </si>
+  <si>
+    <t>Identifier.extension</t>
+  </si>
+  <si>
+    <t>http://fhir.de/sid/arge-ik/iknr</t>
+  </si>
+  <si>
+    <t>identifier-kvid-10</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-kvid-10</t>
+  </si>
+  <si>
+    <t>IdentifierKvid10</t>
+  </si>
+  <si>
+    <t>Identifier KVID-10</t>
+  </si>
+  <si>
+    <t>Identifier profil für die Krankenversichertennummer (KVID-10)</t>
+  </si>
+  <si>
+    <t>identifier-telematik-id</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-telematik-id</t>
+  </si>
+  <si>
+    <t>IdentifierTelematikId</t>
+  </si>
+  <si>
+    <t>Identifier Telematik-ID</t>
+  </si>
+  <si>
+    <t>Identifier profil für die Telematik-ID</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/sid/telematik-id</t>
   </si>
 </sst>
 </file>
@@ -3528,7 +3577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B127"/>
+  <dimension ref="A1:B190"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -4364,7 +4413,7 @@
         <v>2</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="109">
@@ -4372,7 +4421,7 @@
         <v>4</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="110">
@@ -4388,7 +4437,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>999</v>
+        <v>994</v>
       </c>
     </row>
     <row r="112">
@@ -4396,7 +4445,7 @@
         <v>10</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="113">
@@ -4452,7 +4501,7 @@
         <v>23</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>1001</v>
+        <v>996</v>
       </c>
     </row>
     <row r="120">
@@ -4488,7 +4537,7 @@
         <v>30</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>1002</v>
+        <v>997</v>
       </c>
     </row>
     <row r="125">
@@ -4496,7 +4545,7 @@
         <v>32</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="126">
@@ -4512,6 +4561,492 @@
         <v>35</v>
       </c>
       <c r="B127" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B128" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B135" s="2"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B141" s="2"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B142" s="2"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B149" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B162" s="2"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B163" s="2"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B170" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B177" s="2"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B183" s="2"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B184" s="2"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B190" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -4522,7 +5057,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK424"/>
+  <dimension ref="A1:AK451"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.921875" customWidth="true" bestFit="true"/>
@@ -4544,7 +5079,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="58.41796875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="15.11328125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="47.265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
@@ -36927,7 +37462,7 @@
         <v>75</v>
       </c>
       <c r="T309" t="s" s="2">
-        <v>843</v>
+        <v>75</v>
       </c>
       <c r="U309" t="s" s="2">
         <v>75</v>
@@ -36948,7 +37483,7 @@
         <v>282</v>
       </c>
       <c r="AA309" t="s" s="2">
-        <v>844</v>
+        <v>283</v>
       </c>
       <c r="AB309" t="s" s="2">
         <v>75</v>
@@ -36978,7 +37513,7 @@
         <v>81</v>
       </c>
       <c r="AK309" t="s" s="2">
-        <v>845</v>
+        <v>119</v>
       </c>
     </row>
     <row r="310">
@@ -36986,10 +37521,10 @@
         <v>766</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
@@ -36997,7 +37532,7 @@
       </c>
       <c r="F310" s="2"/>
       <c r="G310" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H310" t="s" s="2">
         <v>84</v>
@@ -37031,7 +37566,7 @@
       </c>
       <c r="R310" s="2"/>
       <c r="S310" t="s" s="2">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="T310" t="s" s="2">
         <v>75</v>
@@ -37093,10 +37628,10 @@
         <v>766</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -37104,7 +37639,7 @@
       </c>
       <c r="F311" s="2"/>
       <c r="G311" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H311" t="s" s="2">
         <v>84</v>
@@ -37190,7 +37725,7 @@
         <v>75</v>
       </c>
       <c r="AK311" t="s" s="2">
-        <v>849</v>
+        <v>119</v>
       </c>
     </row>
     <row r="312">
@@ -37198,10 +37733,10 @@
         <v>766</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
@@ -37303,10 +37838,10 @@
         <v>766</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -37329,7 +37864,7 @@
         <v>150</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>852</v>
+        <v>311</v>
       </c>
       <c r="M313" t="s" s="2">
         <v>312</v>
@@ -37408,10 +37943,10 @@
         <v>766</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -37511,10 +38046,10 @@
         <v>766</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -37616,10 +38151,10 @@
         <v>766</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
@@ -37721,10 +38256,10 @@
         <v>766</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -37826,10 +38361,10 @@
         <v>766</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -37852,7 +38387,7 @@
         <v>150</v>
       </c>
       <c r="L318" t="s" s="2">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="M318" t="s" s="2">
         <v>429</v>
@@ -37931,10 +38466,10 @@
         <v>766</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -38036,10 +38571,10 @@
         <v>766</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -38141,10 +38676,10 @@
         <v>766</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -38170,13 +38705,13 @@
         <v>521</v>
       </c>
       <c r="M321" t="s" s="2">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="N321" t="s" s="2">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="O321" t="s" s="2">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="P321" s="2"/>
       <c r="Q321" t="s" s="2">
@@ -38226,7 +38761,7 @@
         <v>75</v>
       </c>
       <c r="AG321" t="s" s="2">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="AH321" t="s" s="2">
         <v>76</v>
@@ -38246,14 +38781,14 @@
         <v>766</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" t="s" s="2">
@@ -38272,16 +38807,16 @@
         <v>150</v>
       </c>
       <c r="L322" t="s" s="2">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="M322" t="s" s="2">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="N322" t="s" s="2">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O322" t="s" s="2">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="P322" s="2"/>
       <c r="Q322" t="s" s="2">
@@ -38331,7 +38866,7 @@
         <v>75</v>
       </c>
       <c r="AG322" t="s" s="2">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="AH322" t="s" s="2">
         <v>76</v>
@@ -38351,14 +38886,14 @@
         <v>766</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="F323" s="2"/>
       <c r="G323" t="s" s="2">
@@ -38380,10 +38915,10 @@
         <v>311</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="O323" t="s" s="2">
         <v>351</v>
@@ -38436,7 +38971,7 @@
         <v>75</v>
       </c>
       <c r="AG323" t="s" s="2">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="AH323" t="s" s="2">
         <v>76</v>
@@ -38456,10 +38991,10 @@
         <v>766</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -38482,16 +39017,16 @@
         <v>150</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="N324" t="s" s="2">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="O324" t="s" s="2">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="P324" s="2"/>
       <c r="Q324" t="s" s="2">
@@ -38541,7 +39076,7 @@
         <v>75</v>
       </c>
       <c r="AG324" t="s" s="2">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="AH324" t="s" s="2">
         <v>76</v>
@@ -38561,10 +39096,10 @@
         <v>766</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -38590,10 +39125,10 @@
         <v>451</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="N325" t="s" s="2">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="O325" s="2"/>
       <c r="P325" s="2"/>
@@ -38644,7 +39179,7 @@
         <v>75</v>
       </c>
       <c r="AG325" t="s" s="2">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="AH325" t="s" s="2">
         <v>76</v>
@@ -38664,10 +39199,10 @@
         <v>766</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -38767,10 +39302,10 @@
         <v>766</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -38872,10 +39407,10 @@
         <v>766</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -38979,10 +39514,10 @@
         <v>766</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -39008,10 +39543,10 @@
         <v>108</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="N329" t="s" s="2">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="O329" t="s" s="2">
         <v>333</v>
@@ -39064,7 +39599,7 @@
         <v>75</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>76</v>
@@ -39073,7 +39608,7 @@
         <v>84</v>
       </c>
       <c r="AJ329" t="s" s="2">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="AK329" t="s" s="2">
         <v>119</v>
@@ -39084,10 +39619,10 @@
         <v>766</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
@@ -39113,13 +39648,13 @@
         <v>108</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="O330" t="s" s="2">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="P330" s="2"/>
       <c r="Q330" t="s" s="2">
@@ -39169,7 +39704,7 @@
         <v>75</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>76</v>
@@ -39178,7 +39713,7 @@
         <v>84</v>
       </c>
       <c r="AJ330" t="s" s="2">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="AK330" t="s" s="2">
         <v>119</v>
@@ -39189,10 +39724,10 @@
         <v>766</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -39218,16 +39753,16 @@
         <v>277</v>
       </c>
       <c r="M331" t="s" s="2">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="N331" t="s" s="2">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="O331" t="s" s="2">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="P331" t="s" s="2">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="Q331" t="s" s="2">
         <v>75</v>
@@ -39256,7 +39791,7 @@
       </c>
       <c r="Z331" s="2"/>
       <c r="AA331" t="s" s="2">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="AB331" t="s" s="2">
         <v>75</v>
@@ -39274,7 +39809,7 @@
         <v>75</v>
       </c>
       <c r="AG331" t="s" s="2">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="AH331" t="s" s="2">
         <v>76</v>
@@ -39283,7 +39818,7 @@
         <v>84</v>
       </c>
       <c r="AJ331" t="s" s="2">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="AK331" t="s" s="2">
         <v>119</v>
@@ -39294,10 +39829,10 @@
         <v>766</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -39323,10 +39858,10 @@
         <v>451</v>
       </c>
       <c r="M332" t="s" s="2">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="N332" t="s" s="2">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="O332" s="2"/>
       <c r="P332" s="2"/>
@@ -39377,7 +39912,7 @@
         <v>75</v>
       </c>
       <c r="AG332" t="s" s="2">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="AH332" t="s" s="2">
         <v>76</v>
@@ -39397,10 +39932,10 @@
         <v>766</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -39500,10 +40035,10 @@
         <v>766</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -39605,10 +40140,10 @@
         <v>766</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -39712,10 +40247,10 @@
         <v>766</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -39741,10 +40276,10 @@
         <v>115</v>
       </c>
       <c r="M336" t="s" s="2">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="N336" t="s" s="2">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="O336" s="2"/>
       <c r="P336" s="2"/>
@@ -39795,7 +40330,7 @@
         <v>75</v>
       </c>
       <c r="AG336" t="s" s="2">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="AH336" t="s" s="2">
         <v>84</v>
@@ -39815,10 +40350,10 @@
         <v>766</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -39841,13 +40376,13 @@
         <v>75</v>
       </c>
       <c r="L337" t="s" s="2">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="M337" t="s" s="2">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="N337" t="s" s="2">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="O337" t="s" s="2">
         <v>351</v>
@@ -39900,7 +40435,7 @@
         <v>75</v>
       </c>
       <c r="AG337" t="s" s="2">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="AH337" t="s" s="2">
         <v>76</v>
@@ -39920,10 +40455,10 @@
         <v>766</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -39949,10 +40484,10 @@
         <v>521</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="N338" t="s" s="2">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="O338" s="2"/>
       <c r="P338" s="2"/>
@@ -40003,7 +40538,7 @@
         <v>75</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>76</v>
@@ -40023,10 +40558,10 @@
         <v>766</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -40052,10 +40587,10 @@
         <v>451</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="O339" s="2"/>
       <c r="P339" s="2"/>
@@ -40106,7 +40641,7 @@
         <v>75</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>76</v>
@@ -40126,10 +40661,10 @@
         <v>766</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -40229,10 +40764,10 @@
         <v>766</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -40334,10 +40869,10 @@
         <v>766</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
@@ -40441,10 +40976,10 @@
         <v>766</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
@@ -40470,10 +41005,10 @@
         <v>217</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="O343" s="2"/>
       <c r="P343" s="2"/>
@@ -40503,10 +41038,10 @@
         <v>271</v>
       </c>
       <c r="Z343" t="s" s="2">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="AA343" t="s" s="2">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="AB343" t="s" s="2">
         <v>75</v>
@@ -40524,7 +41059,7 @@
         <v>75</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>76</v>
@@ -40544,10 +41079,10 @@
         <v>766</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -40573,10 +41108,10 @@
         <v>303</v>
       </c>
       <c r="M344" t="s" s="2">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="N344" t="s" s="2">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="O344" t="s" s="2">
         <v>306</v>
@@ -40629,7 +41164,7 @@
         <v>75</v>
       </c>
       <c r="AG344" t="s" s="2">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="AH344" t="s" s="2">
         <v>76</v>
@@ -40649,10 +41184,10 @@
         <v>766</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -40678,10 +41213,10 @@
         <v>451</v>
       </c>
       <c r="M345" t="s" s="2">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="N345" t="s" s="2">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="O345" s="2"/>
       <c r="P345" s="2"/>
@@ -40689,7 +41224,7 @@
         <v>75</v>
       </c>
       <c r="R345" t="s" s="2">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="S345" t="s" s="2">
         <v>75</v>
@@ -40734,7 +41269,7 @@
         <v>75</v>
       </c>
       <c r="AG345" t="s" s="2">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="AH345" t="s" s="2">
         <v>76</v>
@@ -40754,10 +41289,10 @@
         <v>766</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -40857,10 +41392,10 @@
         <v>766</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -40962,10 +41497,10 @@
         <v>766</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
@@ -41069,10 +41604,10 @@
         <v>766</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -41098,10 +41633,10 @@
         <v>277</v>
       </c>
       <c r="M349" t="s" s="2">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="N349" t="s" s="2">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="O349" t="s" s="2">
         <v>357</v>
@@ -41133,10 +41668,10 @@
         <v>199</v>
       </c>
       <c r="Z349" t="s" s="2">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="AA349" t="s" s="2">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="AB349" t="s" s="2">
         <v>75</v>
@@ -41154,7 +41689,7 @@
         <v>75</v>
       </c>
       <c r="AG349" t="s" s="2">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="AH349" t="s" s="2">
         <v>84</v>
@@ -41174,10 +41709,10 @@
         <v>766</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -41200,13 +41735,13 @@
         <v>75</v>
       </c>
       <c r="L350" t="s" s="2">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="M350" t="s" s="2">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="N350" t="s" s="2">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="O350" t="s" s="2">
         <v>351</v>
@@ -41259,7 +41794,7 @@
         <v>75</v>
       </c>
       <c r="AG350" t="s" s="2">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="AH350" t="s" s="2">
         <v>84</v>
@@ -41279,10 +41814,10 @@
         <v>766</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -41308,20 +41843,20 @@
         <v>277</v>
       </c>
       <c r="M351" t="s" s="2">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="N351" t="s" s="2">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="O351" t="s" s="2">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="P351" s="2"/>
       <c r="Q351" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R351" t="s" s="2">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="S351" t="s" s="2">
         <v>75</v>
@@ -41345,10 +41880,10 @@
         <v>207</v>
       </c>
       <c r="Z351" t="s" s="2">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="AA351" t="s" s="2">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="AB351" t="s" s="2">
         <v>75</v>
@@ -41366,7 +41901,7 @@
         <v>75</v>
       </c>
       <c r="AG351" t="s" s="2">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="AH351" t="s" s="2">
         <v>76</v>
@@ -41386,10 +41921,10 @@
         <v>766</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -41415,13 +41950,13 @@
         <v>195</v>
       </c>
       <c r="M352" t="s" s="2">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="N352" t="s" s="2">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="O352" t="s" s="2">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="P352" s="2"/>
       <c r="Q352" t="s" s="2">
@@ -41471,7 +42006,7 @@
         <v>75</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="AH352" t="s" s="2">
         <v>76</v>
@@ -41491,10 +42026,10 @@
         <v>766</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -41520,13 +42055,13 @@
         <v>195</v>
       </c>
       <c r="M353" t="s" s="2">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="N353" t="s" s="2">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="O353" t="s" s="2">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="P353" s="2"/>
       <c r="Q353" t="s" s="2">
@@ -41555,10 +42090,10 @@
         <v>199</v>
       </c>
       <c r="Z353" t="s" s="2">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="AA353" t="s" s="2">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="AB353" t="s" s="2">
         <v>75</v>
@@ -41576,7 +42111,7 @@
         <v>75</v>
       </c>
       <c r="AG353" t="s" s="2">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>76</v>
@@ -41596,10 +42131,10 @@
         <v>766</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" t="s" s="2">
@@ -41625,13 +42160,13 @@
         <v>195</v>
       </c>
       <c r="M354" t="s" s="2">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="N354" t="s" s="2">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="O354" t="s" s="2">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="P354" s="2"/>
       <c r="Q354" t="s" s="2">
@@ -41660,10 +42195,10 @@
         <v>199</v>
       </c>
       <c r="Z354" t="s" s="2">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="AA354" t="s" s="2">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="AB354" t="s" s="2">
         <v>75</v>
@@ -41681,7 +42216,7 @@
         <v>75</v>
       </c>
       <c r="AG354" t="s" s="2">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="AH354" t="s" s="2">
         <v>76</v>
@@ -41701,10 +42236,10 @@
         <v>766</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -41730,13 +42265,13 @@
         <v>277</v>
       </c>
       <c r="M355" t="s" s="2">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="N355" t="s" s="2">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="O355" t="s" s="2">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="P355" s="2"/>
       <c r="Q355" t="s" s="2">
@@ -41765,10 +42300,10 @@
         <v>207</v>
       </c>
       <c r="Z355" t="s" s="2">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="AA355" t="s" s="2">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="AB355" t="s" s="2">
         <v>75</v>
@@ -41786,7 +42321,7 @@
         <v>75</v>
       </c>
       <c r="AG355" t="s" s="2">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="AH355" t="s" s="2">
         <v>76</v>
@@ -41806,10 +42341,10 @@
         <v>766</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -41835,13 +42370,13 @@
         <v>303</v>
       </c>
       <c r="M356" t="s" s="2">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="N356" t="s" s="2">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="O356" t="s" s="2">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="P356" s="2"/>
       <c r="Q356" t="s" s="2">
@@ -41891,7 +42426,7 @@
         <v>75</v>
       </c>
       <c r="AG356" t="s" s="2">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="AH356" t="s" s="2">
         <v>76</v>
@@ -41911,10 +42446,10 @@
         <v>766</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -41940,10 +42475,10 @@
         <v>451</v>
       </c>
       <c r="M357" t="s" s="2">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="N357" t="s" s="2">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="O357" s="2"/>
       <c r="P357" s="2"/>
@@ -41951,7 +42486,7 @@
         <v>75</v>
       </c>
       <c r="R357" t="s" s="2">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="S357" t="s" s="2">
         <v>75</v>
@@ -41996,7 +42531,7 @@
         <v>75</v>
       </c>
       <c r="AG357" t="s" s="2">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="AH357" t="s" s="2">
         <v>76</v>
@@ -42016,10 +42551,10 @@
         <v>766</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
@@ -42119,10 +42654,10 @@
         <v>766</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -42224,10 +42759,10 @@
         <v>766</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -42331,10 +42866,10 @@
         <v>766</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -42360,10 +42895,10 @@
         <v>217</v>
       </c>
       <c r="M361" t="s" s="2">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="N361" t="s" s="2">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="O361" s="2"/>
       <c r="P361" s="2"/>
@@ -42393,10 +42928,10 @@
         <v>271</v>
       </c>
       <c r="Z361" t="s" s="2">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="AA361" t="s" s="2">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="AB361" t="s" s="2">
         <v>75</v>
@@ -42414,7 +42949,7 @@
         <v>75</v>
       </c>
       <c r="AG361" t="s" s="2">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="AH361" t="s" s="2">
         <v>84</v>
@@ -42434,10 +42969,10 @@
         <v>766</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -42463,10 +42998,10 @@
         <v>553</v>
       </c>
       <c r="M362" t="s" s="2">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="N362" t="s" s="2">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="O362" t="s" s="2">
         <v>351</v>
@@ -42519,7 +43054,7 @@
         <v>75</v>
       </c>
       <c r="AG362" t="s" s="2">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="AH362" t="s" s="2">
         <v>84</v>
@@ -42539,10 +43074,10 @@
         <v>766</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -42568,10 +43103,10 @@
         <v>78</v>
       </c>
       <c r="M363" t="s" s="2">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="N363" t="s" s="2">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="O363" s="2"/>
       <c r="P363" s="2"/>
@@ -42622,7 +43157,7 @@
         <v>75</v>
       </c>
       <c r="AG363" t="s" s="2">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="AH363" t="s" s="2">
         <v>76</v>
@@ -42639,13 +43174,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
+        <v>992</v>
+      </c>
+      <c r="B364" t="s" s="2">
         <v>997</v>
       </c>
-      <c r="B364" t="s" s="2">
-        <v>1002</v>
-      </c>
       <c r="C364" t="s" s="2">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
@@ -42671,13 +43206,13 @@
         <v>78</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="O364" t="s" s="2">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="P364" s="2"/>
       <c r="Q364" t="s" s="2">
@@ -42727,7 +43262,7 @@
         <v>75</v>
       </c>
       <c r="AG364" t="s" s="2">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="AH364" t="s" s="2">
         <v>76</v>
@@ -42744,13 +43279,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -42849,13 +43384,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -42952,13 +43487,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -43055,13 +43590,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -43160,13 +43695,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -43265,13 +43800,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -43370,13 +43905,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -43475,13 +44010,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -43580,13 +44115,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="D373" t="s" s="2">
         <v>192</v>
@@ -43628,7 +44163,7 @@
       </c>
       <c r="R373" s="2"/>
       <c r="S373" t="s" s="2">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="T373" t="s" s="2">
         <v>75</v>
@@ -43687,13 +44222,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -43792,13 +44327,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -43897,13 +44432,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -44002,13 +44537,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -44107,13 +44642,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -44139,10 +44674,10 @@
         <v>451</v>
       </c>
       <c r="M378" t="s" s="2">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="N378" t="s" s="2">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="O378" s="2"/>
       <c r="P378" s="2"/>
@@ -44181,7 +44716,7 @@
         <v>75</v>
       </c>
       <c r="AC378" t="s" s="2">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="AD378" s="2"/>
       <c r="AE378" t="s" s="2">
@@ -44191,7 +44726,7 @@
         <v>95</v>
       </c>
       <c r="AG378" t="s" s="2">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="AH378" t="s" s="2">
         <v>76</v>
@@ -44203,18 +44738,18 @@
         <v>81</v>
       </c>
       <c r="AK378" t="s" s="2">
-        <v>1025</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -44311,13 +44846,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -44416,13 +44951,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -44523,13 +45058,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
@@ -44555,10 +45090,10 @@
         <v>85</v>
       </c>
       <c r="M382" t="s" s="2">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="N382" t="s" s="2">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="O382" t="s" s="2">
         <v>391</v>
@@ -44611,7 +45146,7 @@
         <v>75</v>
       </c>
       <c r="AG382" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="AH382" t="s" s="2">
         <v>84</v>
@@ -44628,13 +45163,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -44660,10 +45195,10 @@
         <v>138</v>
       </c>
       <c r="M383" t="s" s="2">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="N383" t="s" s="2">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="O383" s="2"/>
       <c r="P383" s="2"/>
@@ -44714,7 +45249,7 @@
         <v>75</v>
       </c>
       <c r="AG383" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="AH383" t="s" s="2">
         <v>76</v>
@@ -44723,7 +45258,7 @@
         <v>84</v>
       </c>
       <c r="AJ383" t="s" s="2">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="AK383" t="s" s="2">
         <v>119</v>
@@ -44731,13 +45266,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -44763,13 +45298,13 @@
         <v>234</v>
       </c>
       <c r="M384" t="s" s="2">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="N384" t="s" s="2">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="O384" t="s" s="2">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="P384" s="2"/>
       <c r="Q384" t="s" s="2">
@@ -44819,7 +45354,7 @@
         <v>75</v>
       </c>
       <c r="AG384" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="AH384" t="s" s="2">
         <v>76</v>
@@ -44828,7 +45363,7 @@
         <v>84</v>
       </c>
       <c r="AJ384" t="s" s="2">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AK384" t="s" s="2">
         <v>75</v>
@@ -44836,13 +45371,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -44868,13 +45403,13 @@
         <v>75</v>
       </c>
       <c r="M385" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N385" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O385" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P385" s="2"/>
       <c r="Q385" t="s" s="2">
@@ -44924,7 +45459,7 @@
         <v>75</v>
       </c>
       <c r="AG385" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH385" t="s" s="2">
         <v>76</v>
@@ -44941,13 +45476,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="D386" t="s" s="2">
         <v>242</v>
@@ -44975,10 +45510,10 @@
         <v>451</v>
       </c>
       <c r="M386" t="s" s="2">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="N386" t="s" s="2">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
@@ -45029,7 +45564,7 @@
         <v>75</v>
       </c>
       <c r="AG386" t="s" s="2">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="AH386" t="s" s="2">
         <v>76</v>
@@ -45041,18 +45576,18 @@
         <v>81</v>
       </c>
       <c r="AK386" t="s" s="2">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -45149,13 +45684,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
@@ -45254,13 +45789,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -45361,13 +45896,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -45393,10 +45928,10 @@
         <v>85</v>
       </c>
       <c r="M390" t="s" s="2">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="N390" t="s" s="2">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="O390" t="s" s="2">
         <v>391</v>
@@ -45449,7 +45984,7 @@
         <v>75</v>
       </c>
       <c r="AG390" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="AH390" t="s" s="2">
         <v>84</v>
@@ -45466,13 +46001,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -45498,10 +46033,10 @@
         <v>138</v>
       </c>
       <c r="M391" t="s" s="2">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="N391" t="s" s="2">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="O391" s="2"/>
       <c r="P391" s="2"/>
@@ -45552,7 +46087,7 @@
         <v>75</v>
       </c>
       <c r="AG391" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="AH391" t="s" s="2">
         <v>76</v>
@@ -45561,7 +46096,7 @@
         <v>84</v>
       </c>
       <c r="AJ391" t="s" s="2">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="AK391" t="s" s="2">
         <v>119</v>
@@ -45569,13 +46104,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" t="s" s="2">
@@ -45601,13 +46136,13 @@
         <v>234</v>
       </c>
       <c r="M392" t="s" s="2">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="N392" t="s" s="2">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="O392" t="s" s="2">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="P392" s="2"/>
       <c r="Q392" t="s" s="2">
@@ -45657,7 +46192,7 @@
         <v>75</v>
       </c>
       <c r="AG392" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="AH392" t="s" s="2">
         <v>76</v>
@@ -45666,7 +46201,7 @@
         <v>84</v>
       </c>
       <c r="AJ392" t="s" s="2">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AK392" t="s" s="2">
         <v>75</v>
@@ -45674,13 +46209,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -45706,13 +46241,13 @@
         <v>75</v>
       </c>
       <c r="M393" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N393" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O393" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P393" s="2"/>
       <c r="Q393" t="s" s="2">
@@ -45750,7 +46285,7 @@
         <v>75</v>
       </c>
       <c r="AC393" t="s" s="2">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="AD393" s="2"/>
       <c r="AE393" t="s" s="2">
@@ -45760,7 +46295,7 @@
         <v>95</v>
       </c>
       <c r="AG393" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH393" t="s" s="2">
         <v>76</v>
@@ -45777,13 +46312,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" t="s" s="2">
@@ -45880,13 +46415,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
@@ -45985,13 +46520,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
@@ -46092,13 +46627,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -46124,10 +46659,10 @@
         <v>85</v>
       </c>
       <c r="M397" t="s" s="2">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="N397" t="s" s="2">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="O397" t="s" s="2">
         <v>391</v>
@@ -46180,7 +46715,7 @@
         <v>75</v>
       </c>
       <c r="AG397" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="AH397" t="s" s="2">
         <v>84</v>
@@ -46197,13 +46732,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" t="s" s="2">
@@ -46229,10 +46764,10 @@
         <v>138</v>
       </c>
       <c r="M398" t="s" s="2">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="N398" t="s" s="2">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="O398" s="2"/>
       <c r="P398" s="2"/>
@@ -46283,7 +46818,7 @@
         <v>75</v>
       </c>
       <c r="AG398" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="AH398" t="s" s="2">
         <v>76</v>
@@ -46292,7 +46827,7 @@
         <v>84</v>
       </c>
       <c r="AJ398" t="s" s="2">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="AK398" t="s" s="2">
         <v>119</v>
@@ -46300,13 +46835,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="D399" s="2"/>
       <c r="E399" t="s" s="2">
@@ -46332,13 +46867,13 @@
         <v>234</v>
       </c>
       <c r="M399" t="s" s="2">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="N399" t="s" s="2">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="O399" t="s" s="2">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="P399" s="2"/>
       <c r="Q399" t="s" s="2">
@@ -46388,7 +46923,7 @@
         <v>75</v>
       </c>
       <c r="AG399" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="AH399" t="s" s="2">
         <v>76</v>
@@ -46397,7 +46932,7 @@
         <v>84</v>
       </c>
       <c r="AJ399" t="s" s="2">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AK399" t="s" s="2">
         <v>75</v>
@@ -46405,13 +46940,13 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" t="s" s="2">
@@ -46437,13 +46972,13 @@
         <v>75</v>
       </c>
       <c r="M400" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N400" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O400" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P400" s="2"/>
       <c r="Q400" t="s" s="2">
@@ -46493,7 +47028,7 @@
         <v>75</v>
       </c>
       <c r="AG400" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH400" t="s" s="2">
         <v>76</v>
@@ -46510,13 +47045,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="D401" t="s" s="2">
         <v>98</v>
@@ -46544,13 +47079,13 @@
         <v>451</v>
       </c>
       <c r="M401" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N401" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O401" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P401" s="2"/>
       <c r="Q401" t="s" s="2">
@@ -46600,7 +47135,7 @@
         <v>75</v>
       </c>
       <c r="AG401" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH401" t="s" s="2">
         <v>76</v>
@@ -46617,13 +47152,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" t="s" s="2">
@@ -46720,13 +47255,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="D403" s="2"/>
       <c r="E403" t="s" s="2">
@@ -46825,13 +47360,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" t="s" s="2">
@@ -46932,13 +47467,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -46964,10 +47499,10 @@
         <v>85</v>
       </c>
       <c r="M405" t="s" s="2">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="N405" t="s" s="2">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="O405" t="s" s="2">
         <v>391</v>
@@ -47020,7 +47555,7 @@
         <v>75</v>
       </c>
       <c r="AG405" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="AH405" t="s" s="2">
         <v>84</v>
@@ -47037,13 +47572,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="D406" s="2"/>
       <c r="E406" t="s" s="2">
@@ -47069,10 +47604,10 @@
         <v>115</v>
       </c>
       <c r="M406" t="s" s="2">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="N406" t="s" s="2">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="O406" s="2"/>
       <c r="P406" s="2"/>
@@ -47123,7 +47658,7 @@
         <v>75</v>
       </c>
       <c r="AG406" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="AH406" t="s" s="2">
         <v>76</v>
@@ -47132,7 +47667,7 @@
         <v>84</v>
       </c>
       <c r="AJ406" t="s" s="2">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="AK406" t="s" s="2">
         <v>119</v>
@@ -47140,13 +47675,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -47172,13 +47707,13 @@
         <v>234</v>
       </c>
       <c r="M407" t="s" s="2">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="N407" t="s" s="2">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="O407" t="s" s="2">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="P407" s="2"/>
       <c r="Q407" t="s" s="2">
@@ -47228,7 +47763,7 @@
         <v>75</v>
       </c>
       <c r="AG407" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="AH407" t="s" s="2">
         <v>76</v>
@@ -47237,7 +47772,7 @@
         <v>84</v>
       </c>
       <c r="AJ407" t="s" s="2">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AK407" t="s" s="2">
         <v>75</v>
@@ -47245,13 +47780,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="D408" s="2"/>
       <c r="E408" t="s" s="2">
@@ -47277,13 +47812,13 @@
         <v>75</v>
       </c>
       <c r="M408" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N408" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O408" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P408" s="2"/>
       <c r="Q408" t="s" s="2">
@@ -47333,7 +47868,7 @@
         <v>75</v>
       </c>
       <c r="AG408" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH408" t="s" s="2">
         <v>76</v>
@@ -47350,13 +47885,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="D409" t="s" s="2">
         <v>121</v>
@@ -47384,13 +47919,13 @@
         <v>451</v>
       </c>
       <c r="M409" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N409" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O409" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P409" s="2"/>
       <c r="Q409" t="s" s="2">
@@ -47440,7 +47975,7 @@
         <v>75</v>
       </c>
       <c r="AG409" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH409" t="s" s="2">
         <v>76</v>
@@ -47457,13 +47992,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" t="s" s="2">
@@ -47560,13 +48095,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" t="s" s="2">
@@ -47665,13 +48200,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" t="s" s="2">
@@ -47772,13 +48307,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="D413" s="2"/>
       <c r="E413" t="s" s="2">
@@ -47804,10 +48339,10 @@
         <v>85</v>
       </c>
       <c r="M413" t="s" s="2">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="N413" t="s" s="2">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="O413" t="s" s="2">
         <v>391</v>
@@ -47860,7 +48395,7 @@
         <v>75</v>
       </c>
       <c r="AG413" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="AH413" t="s" s="2">
         <v>84</v>
@@ -47877,13 +48412,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" t="s" s="2">
@@ -47909,10 +48444,10 @@
         <v>115</v>
       </c>
       <c r="M414" t="s" s="2">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="N414" t="s" s="2">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="O414" s="2"/>
       <c r="P414" s="2"/>
@@ -47963,7 +48498,7 @@
         <v>75</v>
       </c>
       <c r="AG414" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="AH414" t="s" s="2">
         <v>76</v>
@@ -47972,7 +48507,7 @@
         <v>84</v>
       </c>
       <c r="AJ414" t="s" s="2">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="AK414" t="s" s="2">
         <v>119</v>
@@ -47980,13 +48515,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -48012,13 +48547,13 @@
         <v>234</v>
       </c>
       <c r="M415" t="s" s="2">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="N415" t="s" s="2">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="O415" t="s" s="2">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="P415" s="2"/>
       <c r="Q415" t="s" s="2">
@@ -48068,7 +48603,7 @@
         <v>75</v>
       </c>
       <c r="AG415" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="AH415" t="s" s="2">
         <v>76</v>
@@ -48077,7 +48612,7 @@
         <v>84</v>
       </c>
       <c r="AJ415" t="s" s="2">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AK415" t="s" s="2">
         <v>75</v>
@@ -48085,13 +48620,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -48117,13 +48652,13 @@
         <v>75</v>
       </c>
       <c r="M416" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N416" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O416" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P416" s="2"/>
       <c r="Q416" t="s" s="2">
@@ -48173,7 +48708,7 @@
         <v>75</v>
       </c>
       <c r="AG416" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH416" t="s" s="2">
         <v>76</v>
@@ -48190,13 +48725,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="D417" t="s" s="2">
         <v>130</v>
@@ -48224,13 +48759,13 @@
         <v>451</v>
       </c>
       <c r="M417" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N417" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O417" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P417" s="2"/>
       <c r="Q417" t="s" s="2">
@@ -48280,7 +48815,7 @@
         <v>75</v>
       </c>
       <c r="AG417" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH417" t="s" s="2">
         <v>76</v>
@@ -48297,13 +48832,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -48400,13 +48935,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -48505,13 +49040,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -48612,13 +49147,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" t="s" s="2">
@@ -48644,10 +49179,10 @@
         <v>85</v>
       </c>
       <c r="M421" t="s" s="2">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="N421" t="s" s="2">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="O421" t="s" s="2">
         <v>391</v>
@@ -48700,7 +49235,7 @@
         <v>75</v>
       </c>
       <c r="AG421" t="s" s="2">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="AH421" t="s" s="2">
         <v>84</v>
@@ -48717,13 +49252,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -48749,10 +49284,10 @@
         <v>115</v>
       </c>
       <c r="M422" t="s" s="2">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="N422" t="s" s="2">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="O422" s="2"/>
       <c r="P422" s="2"/>
@@ -48803,7 +49338,7 @@
         <v>75</v>
       </c>
       <c r="AG422" t="s" s="2">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="AH422" t="s" s="2">
         <v>76</v>
@@ -48812,7 +49347,7 @@
         <v>84</v>
       </c>
       <c r="AJ422" t="s" s="2">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="AK422" t="s" s="2">
         <v>119</v>
@@ -48820,13 +49355,13 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" t="s" s="2">
@@ -48852,13 +49387,13 @@
         <v>234</v>
       </c>
       <c r="M423" t="s" s="2">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="N423" t="s" s="2">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="O423" t="s" s="2">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="P423" s="2"/>
       <c r="Q423" t="s" s="2">
@@ -48908,7 +49443,7 @@
         <v>75</v>
       </c>
       <c r="AG423" t="s" s="2">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="AH423" t="s" s="2">
         <v>76</v>
@@ -48917,7 +49452,7 @@
         <v>84</v>
       </c>
       <c r="AJ423" t="s" s="2">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AK423" t="s" s="2">
         <v>75</v>
@@ -48925,13 +49460,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" t="s" s="2">
@@ -48957,13 +49492,13 @@
         <v>75</v>
       </c>
       <c r="M424" t="s" s="2">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="N424" t="s" s="2">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="O424" t="s" s="2">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="P424" s="2"/>
       <c r="Q424" t="s" s="2">
@@ -49013,7 +49548,7 @@
         <v>75</v>
       </c>
       <c r="AG424" t="s" s="2">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="AH424" t="s" s="2">
         <v>76</v>
@@ -49026,6 +49561,2847 @@
       </c>
       <c r="AK424" t="s" s="2">
         <v>75</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B425" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="C425" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="D425" s="2"/>
+      <c r="E425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F425" s="2"/>
+      <c r="G425" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H425" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="M425" t="s" s="2">
+        <v>1095</v>
+      </c>
+      <c r="N425" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="O425" s="2"/>
+      <c r="P425" s="2"/>
+      <c r="Q425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R425" s="2"/>
+      <c r="S425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF425" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG425" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="AH425" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI425" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ425" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK425" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B426" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="C426" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="D426" s="2"/>
+      <c r="E426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F426" s="2"/>
+      <c r="G426" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H426" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L426" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M426" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N426" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O426" s="2"/>
+      <c r="P426" s="2"/>
+      <c r="Q426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R426" s="2"/>
+      <c r="S426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG426" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH426" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI426" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ426" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK426" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B427" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="C427" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="D427" s="2"/>
+      <c r="E427" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F427" s="2"/>
+      <c r="G427" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H427" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L427" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M427" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N427" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O427" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P427" s="2"/>
+      <c r="Q427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R427" s="2"/>
+      <c r="S427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC427" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD427" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AE427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF427" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG427" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AH427" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI427" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ427" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK427" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B428" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C428" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="D428" s="2"/>
+      <c r="E428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F428" s="2"/>
+      <c r="G428" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H428" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J428" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="K428" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L428" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M428" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N428" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O428" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="P428" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Q428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R428" s="2"/>
+      <c r="S428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y428" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z428" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AA428" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AB428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG428" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AH428" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI428" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ428" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK428" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B429" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C429" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="D429" s="2"/>
+      <c r="E429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F429" s="2"/>
+      <c r="G429" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H429" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K429" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L429" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M429" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N429" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O429" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="P429" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="Q429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R429" s="2"/>
+      <c r="S429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y429" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Z429" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA429" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AB429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF429" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG429" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AH429" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI429" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ429" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK429" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B430" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C430" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="D430" s="2"/>
+      <c r="E430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F430" s="2"/>
+      <c r="G430" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H430" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K430" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L430" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M430" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N430" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O430" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="P430" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Q430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R430" s="2"/>
+      <c r="S430" t="s" s="2">
+        <v>1099</v>
+      </c>
+      <c r="T430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U430" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="V430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG430" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AH430" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI430" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ430" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK430" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B431" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C431" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="D431" s="2"/>
+      <c r="E431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F431" s="2"/>
+      <c r="G431" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H431" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K431" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L431" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M431" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N431" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O431" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P431" s="2"/>
+      <c r="Q431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R431" s="2"/>
+      <c r="S431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U431" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="V431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG431" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AH431" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI431" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ431" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK431" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B432" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C432" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="D432" s="2"/>
+      <c r="E432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F432" s="2"/>
+      <c r="G432" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H432" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K432" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L432" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M432" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N432" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O432" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P432" s="2"/>
+      <c r="Q432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R432" s="2"/>
+      <c r="S432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF432" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG432" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AH432" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI432" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ432" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK432" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="B433" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C433" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="D433" s="2"/>
+      <c r="E433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F433" s="2"/>
+      <c r="G433" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H433" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K433" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L433" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M433" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N433" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O433" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P433" s="2"/>
+      <c r="Q433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R433" s="2"/>
+      <c r="S433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF433" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG433" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AH433" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI433" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ433" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK433" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B434" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="C434" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="D434" s="2"/>
+      <c r="E434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F434" s="2"/>
+      <c r="G434" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H434" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="M434" t="s" s="2">
+        <v>1095</v>
+      </c>
+      <c r="N434" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="O434" s="2"/>
+      <c r="P434" s="2"/>
+      <c r="Q434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R434" s="2"/>
+      <c r="S434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF434" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG434" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="AH434" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI434" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ434" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK434" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B435" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="C435" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="D435" s="2"/>
+      <c r="E435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F435" s="2"/>
+      <c r="G435" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H435" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L435" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M435" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N435" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O435" s="2"/>
+      <c r="P435" s="2"/>
+      <c r="Q435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R435" s="2"/>
+      <c r="S435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG435" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH435" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI435" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ435" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK435" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B436" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="C436" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="D436" s="2"/>
+      <c r="E436" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F436" s="2"/>
+      <c r="G436" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H436" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L436" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M436" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N436" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O436" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P436" s="2"/>
+      <c r="Q436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R436" s="2"/>
+      <c r="S436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC436" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD436" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AE436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF436" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG436" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AH436" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI436" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ436" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK436" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B437" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C437" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="D437" s="2"/>
+      <c r="E437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F437" s="2"/>
+      <c r="G437" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H437" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J437" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="K437" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L437" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M437" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N437" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O437" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="P437" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Q437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R437" s="2"/>
+      <c r="S437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y437" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z437" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AA437" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AB437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG437" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AH437" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI437" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ437" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK437" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B438" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C438" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="D438" s="2"/>
+      <c r="E438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F438" s="2"/>
+      <c r="G438" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H438" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K438" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L438" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M438" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N438" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O438" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="P438" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="Q438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R438" s="2"/>
+      <c r="S438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y438" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Z438" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA438" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AB438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF438" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG438" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AH438" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI438" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ438" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK438" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B439" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C439" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="D439" s="2"/>
+      <c r="E439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F439" s="2"/>
+      <c r="G439" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H439" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K439" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L439" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M439" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N439" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O439" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="P439" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Q439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R439" s="2"/>
+      <c r="S439" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="T439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U439" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="V439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG439" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AH439" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI439" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ439" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK439" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B440" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C440" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="D440" s="2"/>
+      <c r="E440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F440" s="2"/>
+      <c r="G440" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H440" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K440" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L440" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M440" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N440" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O440" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P440" s="2"/>
+      <c r="Q440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R440" s="2"/>
+      <c r="S440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U440" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="V440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG440" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AH440" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI440" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ440" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK440" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B441" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C441" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="D441" s="2"/>
+      <c r="E441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F441" s="2"/>
+      <c r="G441" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H441" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K441" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L441" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M441" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N441" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O441" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P441" s="2"/>
+      <c r="Q441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R441" s="2"/>
+      <c r="S441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF441" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG441" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AH441" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI441" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ441" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK441" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B442" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C442" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="D442" s="2"/>
+      <c r="E442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F442" s="2"/>
+      <c r="G442" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H442" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K442" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L442" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M442" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N442" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O442" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P442" s="2"/>
+      <c r="Q442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R442" s="2"/>
+      <c r="S442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF442" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG442" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AH442" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI442" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ442" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK442" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B443" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="C443" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="D443" s="2"/>
+      <c r="E443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F443" s="2"/>
+      <c r="G443" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H443" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L443" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="M443" t="s" s="2">
+        <v>1095</v>
+      </c>
+      <c r="N443" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="O443" s="2"/>
+      <c r="P443" s="2"/>
+      <c r="Q443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R443" s="2"/>
+      <c r="S443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF443" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG443" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="AH443" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI443" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ443" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK443" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B444" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="C444" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="D444" s="2"/>
+      <c r="E444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F444" s="2"/>
+      <c r="G444" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H444" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L444" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M444" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N444" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O444" s="2"/>
+      <c r="P444" s="2"/>
+      <c r="Q444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R444" s="2"/>
+      <c r="S444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG444" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH444" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI444" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ444" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK444" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B445" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="C445" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="D445" s="2"/>
+      <c r="E445" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F445" s="2"/>
+      <c r="G445" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H445" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="L445" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M445" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N445" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O445" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P445" s="2"/>
+      <c r="Q445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R445" s="2"/>
+      <c r="S445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC445" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD445" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AE445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF445" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG445" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AH445" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI445" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ445" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK445" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B446" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C446" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="D446" s="2"/>
+      <c r="E446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F446" s="2"/>
+      <c r="G446" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H446" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J446" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="K446" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L446" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M446" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N446" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O446" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="P446" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Q446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R446" s="2"/>
+      <c r="S446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y446" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z446" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AA446" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AB446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG446" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AH446" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI446" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ446" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK446" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B447" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C447" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="D447" s="2"/>
+      <c r="E447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F447" s="2"/>
+      <c r="G447" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H447" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K447" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L447" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M447" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N447" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O447" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="P447" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="Q447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R447" s="2"/>
+      <c r="S447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y447" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Z447" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA447" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AB447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF447" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG447" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AH447" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI447" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ447" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK447" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B448" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C448" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="D448" s="2"/>
+      <c r="E448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F448" s="2"/>
+      <c r="G448" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H448" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K448" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L448" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M448" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N448" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O448" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="P448" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Q448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R448" s="2"/>
+      <c r="S448" t="s" s="2">
+        <v>1110</v>
+      </c>
+      <c r="T448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U448" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="V448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG448" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AH448" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI448" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ448" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK448" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B449" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C449" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="D449" s="2"/>
+      <c r="E449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F449" s="2"/>
+      <c r="G449" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H449" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K449" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L449" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M449" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N449" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O449" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P449" s="2"/>
+      <c r="Q449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R449" s="2"/>
+      <c r="S449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U449" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="V449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG449" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AH449" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI449" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ449" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK449" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B450" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C450" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="D450" s="2"/>
+      <c r="E450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F450" s="2"/>
+      <c r="G450" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H450" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K450" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L450" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M450" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N450" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O450" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P450" s="2"/>
+      <c r="Q450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R450" s="2"/>
+      <c r="S450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF450" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG450" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AH450" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI450" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ450" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK450" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="B451" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C451" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="D451" s="2"/>
+      <c r="E451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F451" s="2"/>
+      <c r="G451" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H451" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K451" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L451" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M451" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N451" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O451" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P451" s="2"/>
+      <c r="Q451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="R451" s="2"/>
+      <c r="S451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF451" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG451" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AH451" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI451" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ451" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK451" t="s" s="2">
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-25T12:53:52+00:00</t>
+    <t>2026-02-25T15:06:56+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-25T15:06:56+00:00</t>
+    <t>2026-02-25T15:46:18+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-25T15:46:18+00:00</t>
+    <t>2026-02-26T09:19:47+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-26T09:19:47+00:00</t>
+    <t>2026-02-26T10:12:23+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-26T10:12:23+00:00</t>
+    <t>2026-02-27T08:04:50+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-27T08:04:50+00:00</t>
+    <t>2026-02-27T13:41:32+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-27T13:41:32+00:00</t>
+    <t>2026-02-27T14:50:48+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-27T14:50:48+00:00</t>
+    <t>2026-02-27T15:19:26+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-02-27T15:19:26+00:00</t>
+    <t>2026-03-02T08:02:27+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-02T08:02:27+00:00</t>
+    <t>2026-03-02T11:53:36+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-02T11:53:36+00:00</t>
+    <t>2026-03-03T10:14:52+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-03T10:14:52+00:00</t>
+    <t>2026-03-03T12:03:19+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-03T12:03:19+00:00</t>
+    <t>2026-03-03T13:32:32+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-03T13:32:32+00:00</t>
+    <t>2026-03-03T14:15:20+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-03T14:15:20+00:00</t>
+    <t>2026-03-03T14:31:56+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-03T14:31:56+00:00</t>
+    <t>2026-03-03T15:16:40+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-03T15:16:40+00:00</t>
+    <t>2026-03-03T15:50:01+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-03T15:50:01+00:00</t>
+    <t>2026-03-03T23:41:56+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-03T23:41:56+00:00</t>
+    <t>2026-03-04T10:28:14+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T10:28:14+00:00</t>
+    <t>2026-03-04T10:52:48+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T10:52:48+00:00</t>
+    <t>2026-03-04T11:52:29+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T11:52:29+00:00</t>
+    <t>2026-03-04T12:46:59+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T12:46:59+00:00</t>
+    <t>2026-03-04T13:04:58+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T13:04:58+00:00</t>
+    <t>2026-03-04T13:16:06+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T13:16:06+00:00</t>
+    <t>2026-03-04T14:00:20+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T14:00:20+00:00</t>
+    <t>2026-03-04T14:06:40+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T14:06:40+00:00</t>
+    <t>2026-03-04T14:16:37+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T14:16:37+00:00</t>
+    <t>2026-03-04T14:27:48+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -3386,7 +3386,7 @@
     <t>Identifier IKNR</t>
   </si>
   <si>
-    <t>2026-03-04T14:27:48+00:00</t>
+    <t>2026-03-06T10:48:20+00:00</t>
   </si>
   <si>
     <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>

--- a/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15247" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14236" uniqueCount="1092">
   <si>
     <t>Property</t>
   </si>
@@ -1342,7 +1342,7 @@
     <t>ChargeItem.subject.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-kvid-10}
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
 </t>
   </si>
   <si>
@@ -1629,7 +1629,7 @@
     <t>ChargeItem.enterer.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-telematik-id}
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
 </t>
   </si>
   <si>
@@ -2628,6 +2628,21 @@
     <t>Consent.patient.identifier.type</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://fhir.de/CodeSystem/identifier-type-de-basis"/&gt;
+    &lt;code value="KVZ10"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>http://fhir.de/ValueSet/identifier-type-de-basis</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+kvid-2:Die type Codes 'GKV' und 'PKV' haben den Status 'retired', daher sollen diese nicht mehr verwendet werden {($this.coding.exists(system='http://fhir.de/CodeSystem/identifier-type-de-basis' and code='GKV') or $this.coding.exists(system='http://fhir.de/CodeSystem/identifier-type-de-basis' and code='PKV')).not()}</t>
+  </si>
+  <si>
     <t>Consent.patient.identifier.system</t>
   </si>
   <si>
@@ -2637,12 +2652,20 @@
     <t>Consent.patient.identifier.value</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+kvid-1:Der unveränderliche Teil der KVID muss 10-stellig sein und mit einem Großbuchstaben anfangen {matches('^[A-Z][0-9]{9}$')}</t>
+  </si>
+  <si>
     <t>Consent.patient.identifier.period</t>
   </si>
   <si>
     <t>Consent.patient.identifier.assigner</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
     <t>Consent.patient.identifier.assigner.id</t>
   </si>
   <si>
@@ -2658,7 +2681,7 @@
     <t>Consent.patient.identifier.assigner.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-iknr}
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-iknr}
 </t>
   </si>
   <si>
@@ -3372,78 +3395,6 @@
   </si>
   <si>
     <t>Parameters.parameter:markingFlag.part:taxOffice.part</t>
-  </si>
-  <si>
-    <t>identifier-iknr</t>
-  </si>
-  <si>
-    <t>https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-iknr</t>
-  </si>
-  <si>
-    <t>IdentifierIknr</t>
-  </si>
-  <si>
-    <t>Identifier IKNR</t>
-  </si>
-  <si>
-    <t>2026-03-06T10:48:20+00:00</t>
-  </si>
-  <si>
-    <t>Identifier profil für die Institutionskennzeichen-Nummer (IKNR)</t>
-  </si>
-  <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Identifier</t>
-  </si>
-  <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
-  </si>
-  <si>
-    <t>Identifier.id</t>
-  </si>
-  <si>
-    <t>Identifier.extension</t>
-  </si>
-  <si>
-    <t>http://fhir.de/sid/arge-ik/iknr</t>
-  </si>
-  <si>
-    <t>identifier-kvid-10</t>
-  </si>
-  <si>
-    <t>https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-kvid-10</t>
-  </si>
-  <si>
-    <t>IdentifierKvid10</t>
-  </si>
-  <si>
-    <t>Identifier KVID-10</t>
-  </si>
-  <si>
-    <t>Identifier profil für die Krankenversichertennummer (KVID-10)</t>
-  </si>
-  <si>
-    <t>identifier-telematik-id</t>
-  </si>
-  <si>
-    <t>https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-telematik-id</t>
-  </si>
-  <si>
-    <t>IdentifierTelematikId</t>
-  </si>
-  <si>
-    <t>Identifier Telematik-ID</t>
-  </si>
-  <si>
-    <t>Identifier profil für die Telematik-ID</t>
-  </si>
-  <si>
-    <t>https://gematik.de/fhir/sid/telematik-id</t>
   </si>
 </sst>
 </file>
@@ -3577,7 +3528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -4413,7 +4364,7 @@
         <v>2</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
     </row>
     <row r="109">
@@ -4421,7 +4372,7 @@
         <v>4</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>993</v>
+        <v>998</v>
       </c>
     </row>
     <row r="110">
@@ -4437,7 +4388,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="112">
@@ -4445,7 +4396,7 @@
         <v>10</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>995</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="113">
@@ -4501,7 +4452,7 @@
         <v>23</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="120">
@@ -4537,7 +4488,7 @@
         <v>30</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>997</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="125">
@@ -4545,7 +4496,7 @@
         <v>32</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>998</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="126">
@@ -4561,492 +4512,6 @@
         <v>35</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B128" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B135" s="2"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B141" s="2"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B142" s="2"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B149" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B156" s="2"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B162" s="2"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B163" s="2"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B170" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B177" s="2"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B183" s="2"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B184" s="2"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B190" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -5057,7 +4522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK451"/>
+  <dimension ref="A1:AK424"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.921875" customWidth="true" bestFit="true"/>
@@ -5079,7 +4544,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="15.11328125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="58.41796875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="47.265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
@@ -37462,7 +36927,7 @@
         <v>75</v>
       </c>
       <c r="T309" t="s" s="2">
-        <v>75</v>
+        <v>843</v>
       </c>
       <c r="U309" t="s" s="2">
         <v>75</v>
@@ -37483,7 +36948,7 @@
         <v>282</v>
       </c>
       <c r="AA309" t="s" s="2">
-        <v>283</v>
+        <v>844</v>
       </c>
       <c r="AB309" t="s" s="2">
         <v>75</v>
@@ -37513,7 +36978,7 @@
         <v>81</v>
       </c>
       <c r="AK309" t="s" s="2">
-        <v>119</v>
+        <v>845</v>
       </c>
     </row>
     <row r="310">
@@ -37521,10 +36986,10 @@
         <v>766</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
@@ -37532,7 +36997,7 @@
       </c>
       <c r="F310" s="2"/>
       <c r="G310" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H310" t="s" s="2">
         <v>84</v>
@@ -37566,7 +37031,7 @@
       </c>
       <c r="R310" s="2"/>
       <c r="S310" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="T310" t="s" s="2">
         <v>75</v>
@@ -37628,10 +37093,10 @@
         <v>766</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -37639,7 +37104,7 @@
       </c>
       <c r="F311" s="2"/>
       <c r="G311" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H311" t="s" s="2">
         <v>84</v>
@@ -37725,7 +37190,7 @@
         <v>75</v>
       </c>
       <c r="AK311" t="s" s="2">
-        <v>119</v>
+        <v>849</v>
       </c>
     </row>
     <row r="312">
@@ -37733,10 +37198,10 @@
         <v>766</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
@@ -37838,10 +37303,10 @@
         <v>766</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -37864,7 +37329,7 @@
         <v>150</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>311</v>
+        <v>852</v>
       </c>
       <c r="M313" t="s" s="2">
         <v>312</v>
@@ -37943,10 +37408,10 @@
         <v>766</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -38046,10 +37511,10 @@
         <v>766</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -38151,10 +37616,10 @@
         <v>766</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
@@ -38256,10 +37721,10 @@
         <v>766</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -38361,10 +37826,10 @@
         <v>766</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -38387,7 +37852,7 @@
         <v>150</v>
       </c>
       <c r="L318" t="s" s="2">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="M318" t="s" s="2">
         <v>429</v>
@@ -38466,10 +37931,10 @@
         <v>766</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -38571,10 +38036,10 @@
         <v>766</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -38676,10 +38141,10 @@
         <v>766</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -38705,13 +38170,13 @@
         <v>521</v>
       </c>
       <c r="M321" t="s" s="2">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="N321" t="s" s="2">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="O321" t="s" s="2">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="P321" s="2"/>
       <c r="Q321" t="s" s="2">
@@ -38761,7 +38226,7 @@
         <v>75</v>
       </c>
       <c r="AG321" t="s" s="2">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="AH321" t="s" s="2">
         <v>76</v>
@@ -38781,14 +38246,14 @@
         <v>766</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" t="s" s="2">
@@ -38807,16 +38272,16 @@
         <v>150</v>
       </c>
       <c r="L322" t="s" s="2">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="M322" t="s" s="2">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="N322" t="s" s="2">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="O322" t="s" s="2">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="P322" s="2"/>
       <c r="Q322" t="s" s="2">
@@ -38866,7 +38331,7 @@
         <v>75</v>
       </c>
       <c r="AG322" t="s" s="2">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="AH322" t="s" s="2">
         <v>76</v>
@@ -38886,14 +38351,14 @@
         <v>766</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="F323" s="2"/>
       <c r="G323" t="s" s="2">
@@ -38915,10 +38380,10 @@
         <v>311</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="O323" t="s" s="2">
         <v>351</v>
@@ -38971,7 +38436,7 @@
         <v>75</v>
       </c>
       <c r="AG323" t="s" s="2">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="AH323" t="s" s="2">
         <v>76</v>
@@ -38991,10 +38456,10 @@
         <v>766</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -39017,16 +38482,16 @@
         <v>150</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="N324" t="s" s="2">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="O324" t="s" s="2">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="P324" s="2"/>
       <c r="Q324" t="s" s="2">
@@ -39076,7 +38541,7 @@
         <v>75</v>
       </c>
       <c r="AG324" t="s" s="2">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="AH324" t="s" s="2">
         <v>76</v>
@@ -39096,10 +38561,10 @@
         <v>766</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -39125,10 +38590,10 @@
         <v>451</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="N325" t="s" s="2">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="O325" s="2"/>
       <c r="P325" s="2"/>
@@ -39179,7 +38644,7 @@
         <v>75</v>
       </c>
       <c r="AG325" t="s" s="2">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="AH325" t="s" s="2">
         <v>76</v>
@@ -39199,10 +38664,10 @@
         <v>766</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -39302,10 +38767,10 @@
         <v>766</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -39407,10 +38872,10 @@
         <v>766</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -39514,10 +38979,10 @@
         <v>766</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -39543,10 +39008,10 @@
         <v>108</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="N329" t="s" s="2">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="O329" t="s" s="2">
         <v>333</v>
@@ -39599,7 +39064,7 @@
         <v>75</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>76</v>
@@ -39608,7 +39073,7 @@
         <v>84</v>
       </c>
       <c r="AJ329" t="s" s="2">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="AK329" t="s" s="2">
         <v>119</v>
@@ -39619,10 +39084,10 @@
         <v>766</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
@@ -39648,13 +39113,13 @@
         <v>108</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="O330" t="s" s="2">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="P330" s="2"/>
       <c r="Q330" t="s" s="2">
@@ -39704,7 +39169,7 @@
         <v>75</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>76</v>
@@ -39713,7 +39178,7 @@
         <v>84</v>
       </c>
       <c r="AJ330" t="s" s="2">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="AK330" t="s" s="2">
         <v>119</v>
@@ -39724,10 +39189,10 @@
         <v>766</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -39753,16 +39218,16 @@
         <v>277</v>
       </c>
       <c r="M331" t="s" s="2">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="N331" t="s" s="2">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="O331" t="s" s="2">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="P331" t="s" s="2">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="Q331" t="s" s="2">
         <v>75</v>
@@ -39791,26 +39256,26 @@
       </c>
       <c r="Z331" s="2"/>
       <c r="AA331" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="AB331" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC331" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD331" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE331" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF331" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG331" t="s" s="2">
         <v>893</v>
       </c>
-      <c r="AB331" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC331" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD331" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE331" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF331" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG331" t="s" s="2">
-        <v>888</v>
-      </c>
       <c r="AH331" t="s" s="2">
         <v>76</v>
       </c>
@@ -39818,7 +39283,7 @@
         <v>84</v>
       </c>
       <c r="AJ331" t="s" s="2">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="AK331" t="s" s="2">
         <v>119</v>
@@ -39829,10 +39294,10 @@
         <v>766</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -39858,10 +39323,10 @@
         <v>451</v>
       </c>
       <c r="M332" t="s" s="2">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="N332" t="s" s="2">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="O332" s="2"/>
       <c r="P332" s="2"/>
@@ -39912,7 +39377,7 @@
         <v>75</v>
       </c>
       <c r="AG332" t="s" s="2">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="AH332" t="s" s="2">
         <v>76</v>
@@ -39932,10 +39397,10 @@
         <v>766</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -40035,10 +39500,10 @@
         <v>766</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -40140,10 +39605,10 @@
         <v>766</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -40247,10 +39712,10 @@
         <v>766</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -40276,10 +39741,10 @@
         <v>115</v>
       </c>
       <c r="M336" t="s" s="2">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="N336" t="s" s="2">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="O336" s="2"/>
       <c r="P336" s="2"/>
@@ -40330,7 +39795,7 @@
         <v>75</v>
       </c>
       <c r="AG336" t="s" s="2">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="AH336" t="s" s="2">
         <v>84</v>
@@ -40350,10 +39815,10 @@
         <v>766</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -40376,13 +39841,13 @@
         <v>75</v>
       </c>
       <c r="L337" t="s" s="2">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="M337" t="s" s="2">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="N337" t="s" s="2">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="O337" t="s" s="2">
         <v>351</v>
@@ -40435,7 +39900,7 @@
         <v>75</v>
       </c>
       <c r="AG337" t="s" s="2">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="AH337" t="s" s="2">
         <v>76</v>
@@ -40455,10 +39920,10 @@
         <v>766</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -40484,10 +39949,10 @@
         <v>521</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="N338" t="s" s="2">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="O338" s="2"/>
       <c r="P338" s="2"/>
@@ -40538,7 +40003,7 @@
         <v>75</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>76</v>
@@ -40558,10 +40023,10 @@
         <v>766</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -40587,10 +40052,10 @@
         <v>451</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="O339" s="2"/>
       <c r="P339" s="2"/>
@@ -40641,7 +40106,7 @@
         <v>75</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>76</v>
@@ -40661,10 +40126,10 @@
         <v>766</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -40764,10 +40229,10 @@
         <v>766</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -40869,10 +40334,10 @@
         <v>766</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
@@ -40976,10 +40441,10 @@
         <v>766</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
@@ -41005,10 +40470,10 @@
         <v>217</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="O343" s="2"/>
       <c r="P343" s="2"/>
@@ -41038,10 +40503,10 @@
         <v>271</v>
       </c>
       <c r="Z343" t="s" s="2">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="AA343" t="s" s="2">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="AB343" t="s" s="2">
         <v>75</v>
@@ -41059,7 +40524,7 @@
         <v>75</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>76</v>
@@ -41079,10 +40544,10 @@
         <v>766</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -41108,10 +40573,10 @@
         <v>303</v>
       </c>
       <c r="M344" t="s" s="2">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="N344" t="s" s="2">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="O344" t="s" s="2">
         <v>306</v>
@@ -41164,7 +40629,7 @@
         <v>75</v>
       </c>
       <c r="AG344" t="s" s="2">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="AH344" t="s" s="2">
         <v>76</v>
@@ -41184,10 +40649,10 @@
         <v>766</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -41213,10 +40678,10 @@
         <v>451</v>
       </c>
       <c r="M345" t="s" s="2">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="N345" t="s" s="2">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="O345" s="2"/>
       <c r="P345" s="2"/>
@@ -41224,7 +40689,7 @@
         <v>75</v>
       </c>
       <c r="R345" t="s" s="2">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="S345" t="s" s="2">
         <v>75</v>
@@ -41269,7 +40734,7 @@
         <v>75</v>
       </c>
       <c r="AG345" t="s" s="2">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="AH345" t="s" s="2">
         <v>76</v>
@@ -41289,10 +40754,10 @@
         <v>766</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -41392,10 +40857,10 @@
         <v>766</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -41497,10 +40962,10 @@
         <v>766</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
@@ -41604,10 +41069,10 @@
         <v>766</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -41633,10 +41098,10 @@
         <v>277</v>
       </c>
       <c r="M349" t="s" s="2">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="N349" t="s" s="2">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="O349" t="s" s="2">
         <v>357</v>
@@ -41668,10 +41133,10 @@
         <v>199</v>
       </c>
       <c r="Z349" t="s" s="2">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="AA349" t="s" s="2">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="AB349" t="s" s="2">
         <v>75</v>
@@ -41689,7 +41154,7 @@
         <v>75</v>
       </c>
       <c r="AG349" t="s" s="2">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="AH349" t="s" s="2">
         <v>84</v>
@@ -41709,10 +41174,10 @@
         <v>766</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -41735,13 +41200,13 @@
         <v>75</v>
       </c>
       <c r="L350" t="s" s="2">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="M350" t="s" s="2">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="N350" t="s" s="2">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="O350" t="s" s="2">
         <v>351</v>
@@ -41794,7 +41259,7 @@
         <v>75</v>
       </c>
       <c r="AG350" t="s" s="2">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="AH350" t="s" s="2">
         <v>84</v>
@@ -41814,10 +41279,10 @@
         <v>766</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -41843,20 +41308,20 @@
         <v>277</v>
       </c>
       <c r="M351" t="s" s="2">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="N351" t="s" s="2">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="O351" t="s" s="2">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="P351" s="2"/>
       <c r="Q351" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R351" t="s" s="2">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="S351" t="s" s="2">
         <v>75</v>
@@ -41880,28 +41345,28 @@
         <v>207</v>
       </c>
       <c r="Z351" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="AA351" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="AB351" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC351" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD351" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE351" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF351" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG351" t="s" s="2">
         <v>946</v>
-      </c>
-      <c r="AA351" t="s" s="2">
-        <v>947</v>
-      </c>
-      <c r="AB351" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC351" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD351" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE351" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF351" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG351" t="s" s="2">
-        <v>941</v>
       </c>
       <c r="AH351" t="s" s="2">
         <v>76</v>
@@ -41921,10 +41386,10 @@
         <v>766</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -41950,13 +41415,13 @@
         <v>195</v>
       </c>
       <c r="M352" t="s" s="2">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="N352" t="s" s="2">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="O352" t="s" s="2">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="P352" s="2"/>
       <c r="Q352" t="s" s="2">
@@ -42006,7 +41471,7 @@
         <v>75</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="AH352" t="s" s="2">
         <v>76</v>
@@ -42026,10 +41491,10 @@
         <v>766</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -42055,13 +41520,13 @@
         <v>195</v>
       </c>
       <c r="M353" t="s" s="2">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="N353" t="s" s="2">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="O353" t="s" s="2">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="P353" s="2"/>
       <c r="Q353" t="s" s="2">
@@ -42090,28 +41555,28 @@
         <v>199</v>
       </c>
       <c r="Z353" t="s" s="2">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="AA353" t="s" s="2">
+        <v>962</v>
+      </c>
+      <c r="AB353" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC353" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD353" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE353" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF353" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG353" t="s" s="2">
         <v>957</v>
-      </c>
-      <c r="AB353" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC353" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD353" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE353" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF353" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG353" t="s" s="2">
-        <v>952</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>76</v>
@@ -42131,10 +41596,10 @@
         <v>766</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" t="s" s="2">
@@ -42160,13 +41625,13 @@
         <v>195</v>
       </c>
       <c r="M354" t="s" s="2">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="N354" t="s" s="2">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="O354" t="s" s="2">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="P354" s="2"/>
       <c r="Q354" t="s" s="2">
@@ -42195,28 +41660,28 @@
         <v>199</v>
       </c>
       <c r="Z354" t="s" s="2">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="AA354" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="AB354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG354" t="s" s="2">
         <v>963</v>
-      </c>
-      <c r="AB354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG354" t="s" s="2">
-        <v>958</v>
       </c>
       <c r="AH354" t="s" s="2">
         <v>76</v>
@@ -42236,10 +41701,10 @@
         <v>766</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -42265,13 +41730,13 @@
         <v>277</v>
       </c>
       <c r="M355" t="s" s="2">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="N355" t="s" s="2">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="O355" t="s" s="2">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="P355" s="2"/>
       <c r="Q355" t="s" s="2">
@@ -42300,28 +41765,28 @@
         <v>207</v>
       </c>
       <c r="Z355" t="s" s="2">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="AA355" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="AB355" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC355" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD355" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE355" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF355" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG355" t="s" s="2">
         <v>969</v>
-      </c>
-      <c r="AB355" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC355" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD355" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE355" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF355" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG355" t="s" s="2">
-        <v>964</v>
       </c>
       <c r="AH355" t="s" s="2">
         <v>76</v>
@@ -42341,10 +41806,10 @@
         <v>766</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -42370,13 +41835,13 @@
         <v>303</v>
       </c>
       <c r="M356" t="s" s="2">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="N356" t="s" s="2">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="O356" t="s" s="2">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="P356" s="2"/>
       <c r="Q356" t="s" s="2">
@@ -42426,7 +41891,7 @@
         <v>75</v>
       </c>
       <c r="AG356" t="s" s="2">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="AH356" t="s" s="2">
         <v>76</v>
@@ -42446,10 +41911,10 @@
         <v>766</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -42475,10 +41940,10 @@
         <v>451</v>
       </c>
       <c r="M357" t="s" s="2">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="N357" t="s" s="2">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="O357" s="2"/>
       <c r="P357" s="2"/>
@@ -42486,7 +41951,7 @@
         <v>75</v>
       </c>
       <c r="R357" t="s" s="2">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="S357" t="s" s="2">
         <v>75</v>
@@ -42531,7 +41996,7 @@
         <v>75</v>
       </c>
       <c r="AG357" t="s" s="2">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="AH357" t="s" s="2">
         <v>76</v>
@@ -42551,10 +42016,10 @@
         <v>766</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
@@ -42654,10 +42119,10 @@
         <v>766</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -42759,10 +42224,10 @@
         <v>766</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -42866,10 +42331,10 @@
         <v>766</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -42895,10 +42360,10 @@
         <v>217</v>
       </c>
       <c r="M361" t="s" s="2">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="N361" t="s" s="2">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="O361" s="2"/>
       <c r="P361" s="2"/>
@@ -42928,10 +42393,10 @@
         <v>271</v>
       </c>
       <c r="Z361" t="s" s="2">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="AA361" t="s" s="2">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="AB361" t="s" s="2">
         <v>75</v>
@@ -42949,7 +42414,7 @@
         <v>75</v>
       </c>
       <c r="AG361" t="s" s="2">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="AH361" t="s" s="2">
         <v>84</v>
@@ -42969,10 +42434,10 @@
         <v>766</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -42998,10 +42463,10 @@
         <v>553</v>
       </c>
       <c r="M362" t="s" s="2">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="N362" t="s" s="2">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="O362" t="s" s="2">
         <v>351</v>
@@ -43054,7 +42519,7 @@
         <v>75</v>
       </c>
       <c r="AG362" t="s" s="2">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="AH362" t="s" s="2">
         <v>84</v>
@@ -43074,10 +42539,10 @@
         <v>766</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -43103,10 +42568,10 @@
         <v>78</v>
       </c>
       <c r="M363" t="s" s="2">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="N363" t="s" s="2">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="O363" s="2"/>
       <c r="P363" s="2"/>
@@ -43157,7 +42622,7 @@
         <v>75</v>
       </c>
       <c r="AG363" t="s" s="2">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="AH363" t="s" s="2">
         <v>76</v>
@@ -43174,13 +42639,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
@@ -43206,13 +42671,13 @@
         <v>78</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="O364" t="s" s="2">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="P364" s="2"/>
       <c r="Q364" t="s" s="2">
@@ -43262,7 +42727,7 @@
         <v>75</v>
       </c>
       <c r="AG364" t="s" s="2">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="AH364" t="s" s="2">
         <v>76</v>
@@ -43279,13 +42744,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -43384,13 +42849,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -43487,13 +42952,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -43590,13 +43055,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -43695,13 +43160,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -43800,13 +43265,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -43905,13 +43370,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -44010,13 +43475,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -44115,13 +43580,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="D373" t="s" s="2">
         <v>192</v>
@@ -44163,7 +43628,7 @@
       </c>
       <c r="R373" s="2"/>
       <c r="S373" t="s" s="2">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="T373" t="s" s="2">
         <v>75</v>
@@ -44222,13 +43687,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -44327,13 +43792,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -44432,13 +43897,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -44537,13 +44002,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -44642,13 +44107,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -44674,10 +44139,10 @@
         <v>451</v>
       </c>
       <c r="M378" t="s" s="2">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="N378" t="s" s="2">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="O378" s="2"/>
       <c r="P378" s="2"/>
@@ -44716,7 +44181,7 @@
         <v>75</v>
       </c>
       <c r="AC378" t="s" s="2">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="AD378" s="2"/>
       <c r="AE378" t="s" s="2">
@@ -44726,7 +44191,7 @@
         <v>95</v>
       </c>
       <c r="AG378" t="s" s="2">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="AH378" t="s" s="2">
         <v>76</v>
@@ -44738,18 +44203,18 @@
         <v>81</v>
       </c>
       <c r="AK378" t="s" s="2">
-        <v>1020</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -44846,13 +44311,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -44951,13 +44416,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -45058,13 +44523,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
@@ -45090,10 +44555,10 @@
         <v>85</v>
       </c>
       <c r="M382" t="s" s="2">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="N382" t="s" s="2">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="O382" t="s" s="2">
         <v>391</v>
@@ -45146,7 +44611,7 @@
         <v>75</v>
       </c>
       <c r="AG382" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="AH382" t="s" s="2">
         <v>84</v>
@@ -45163,13 +44628,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -45195,10 +44660,10 @@
         <v>138</v>
       </c>
       <c r="M383" t="s" s="2">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="N383" t="s" s="2">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="O383" s="2"/>
       <c r="P383" s="2"/>
@@ -45249,7 +44714,7 @@
         <v>75</v>
       </c>
       <c r="AG383" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="AH383" t="s" s="2">
         <v>76</v>
@@ -45258,7 +44723,7 @@
         <v>84</v>
       </c>
       <c r="AJ383" t="s" s="2">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="AK383" t="s" s="2">
         <v>119</v>
@@ -45266,13 +44731,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -45298,13 +44763,13 @@
         <v>234</v>
       </c>
       <c r="M384" t="s" s="2">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="N384" t="s" s="2">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="O384" t="s" s="2">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="P384" s="2"/>
       <c r="Q384" t="s" s="2">
@@ -45354,7 +44819,7 @@
         <v>75</v>
       </c>
       <c r="AG384" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="AH384" t="s" s="2">
         <v>76</v>
@@ -45363,7 +44828,7 @@
         <v>84</v>
       </c>
       <c r="AJ384" t="s" s="2">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="AK384" t="s" s="2">
         <v>75</v>
@@ -45371,13 +44836,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -45403,13 +44868,13 @@
         <v>75</v>
       </c>
       <c r="M385" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N385" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O385" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P385" s="2"/>
       <c r="Q385" t="s" s="2">
@@ -45459,7 +44924,7 @@
         <v>75</v>
       </c>
       <c r="AG385" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH385" t="s" s="2">
         <v>76</v>
@@ -45476,13 +44941,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="D386" t="s" s="2">
         <v>242</v>
@@ -45510,10 +44975,10 @@
         <v>451</v>
       </c>
       <c r="M386" t="s" s="2">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="N386" t="s" s="2">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
@@ -45564,7 +45029,7 @@
         <v>75</v>
       </c>
       <c r="AG386" t="s" s="2">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="AH386" t="s" s="2">
         <v>76</v>
@@ -45576,18 +45041,18 @@
         <v>81</v>
       </c>
       <c r="AK386" t="s" s="2">
-        <v>1041</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -45684,13 +45149,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
@@ -45789,13 +45254,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -45896,13 +45361,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -45928,10 +45393,10 @@
         <v>85</v>
       </c>
       <c r="M390" t="s" s="2">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="N390" t="s" s="2">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="O390" t="s" s="2">
         <v>391</v>
@@ -45984,7 +45449,7 @@
         <v>75</v>
       </c>
       <c r="AG390" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="AH390" t="s" s="2">
         <v>84</v>
@@ -46001,13 +45466,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -46033,10 +45498,10 @@
         <v>138</v>
       </c>
       <c r="M391" t="s" s="2">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="N391" t="s" s="2">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="O391" s="2"/>
       <c r="P391" s="2"/>
@@ -46087,7 +45552,7 @@
         <v>75</v>
       </c>
       <c r="AG391" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="AH391" t="s" s="2">
         <v>76</v>
@@ -46096,7 +45561,7 @@
         <v>84</v>
       </c>
       <c r="AJ391" t="s" s="2">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="AK391" t="s" s="2">
         <v>119</v>
@@ -46104,13 +45569,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" t="s" s="2">
@@ -46136,13 +45601,13 @@
         <v>234</v>
       </c>
       <c r="M392" t="s" s="2">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="N392" t="s" s="2">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="O392" t="s" s="2">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="P392" s="2"/>
       <c r="Q392" t="s" s="2">
@@ -46192,7 +45657,7 @@
         <v>75</v>
       </c>
       <c r="AG392" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="AH392" t="s" s="2">
         <v>76</v>
@@ -46201,7 +45666,7 @@
         <v>84</v>
       </c>
       <c r="AJ392" t="s" s="2">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="AK392" t="s" s="2">
         <v>75</v>
@@ -46209,13 +45674,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -46241,13 +45706,13 @@
         <v>75</v>
       </c>
       <c r="M393" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N393" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O393" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P393" s="2"/>
       <c r="Q393" t="s" s="2">
@@ -46285,7 +45750,7 @@
         <v>75</v>
       </c>
       <c r="AC393" t="s" s="2">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="AD393" s="2"/>
       <c r="AE393" t="s" s="2">
@@ -46295,7 +45760,7 @@
         <v>95</v>
       </c>
       <c r="AG393" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH393" t="s" s="2">
         <v>76</v>
@@ -46312,13 +45777,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" t="s" s="2">
@@ -46415,13 +45880,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
@@ -46520,13 +45985,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
@@ -46627,13 +46092,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -46659,10 +46124,10 @@
         <v>85</v>
       </c>
       <c r="M397" t="s" s="2">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="N397" t="s" s="2">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="O397" t="s" s="2">
         <v>391</v>
@@ -46715,7 +46180,7 @@
         <v>75</v>
       </c>
       <c r="AG397" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="AH397" t="s" s="2">
         <v>84</v>
@@ -46732,13 +46197,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" t="s" s="2">
@@ -46764,10 +46229,10 @@
         <v>138</v>
       </c>
       <c r="M398" t="s" s="2">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="N398" t="s" s="2">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="O398" s="2"/>
       <c r="P398" s="2"/>
@@ -46818,7 +46283,7 @@
         <v>75</v>
       </c>
       <c r="AG398" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="AH398" t="s" s="2">
         <v>76</v>
@@ -46827,7 +46292,7 @@
         <v>84</v>
       </c>
       <c r="AJ398" t="s" s="2">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="AK398" t="s" s="2">
         <v>119</v>
@@ -46835,13 +46300,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="D399" s="2"/>
       <c r="E399" t="s" s="2">
@@ -46867,13 +46332,13 @@
         <v>234</v>
       </c>
       <c r="M399" t="s" s="2">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="N399" t="s" s="2">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="O399" t="s" s="2">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="P399" s="2"/>
       <c r="Q399" t="s" s="2">
@@ -46923,7 +46388,7 @@
         <v>75</v>
       </c>
       <c r="AG399" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="AH399" t="s" s="2">
         <v>76</v>
@@ -46932,7 +46397,7 @@
         <v>84</v>
       </c>
       <c r="AJ399" t="s" s="2">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="AK399" t="s" s="2">
         <v>75</v>
@@ -46940,13 +46405,13 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" t="s" s="2">
@@ -46972,13 +46437,13 @@
         <v>75</v>
       </c>
       <c r="M400" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N400" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O400" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P400" s="2"/>
       <c r="Q400" t="s" s="2">
@@ -47028,7 +46493,7 @@
         <v>75</v>
       </c>
       <c r="AG400" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH400" t="s" s="2">
         <v>76</v>
@@ -47045,13 +46510,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D401" t="s" s="2">
         <v>98</v>
@@ -47079,13 +46544,13 @@
         <v>451</v>
       </c>
       <c r="M401" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N401" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O401" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P401" s="2"/>
       <c r="Q401" t="s" s="2">
@@ -47135,7 +46600,7 @@
         <v>75</v>
       </c>
       <c r="AG401" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH401" t="s" s="2">
         <v>76</v>
@@ -47152,13 +46617,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" t="s" s="2">
@@ -47255,13 +46720,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D403" s="2"/>
       <c r="E403" t="s" s="2">
@@ -47360,13 +46825,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" t="s" s="2">
@@ -47467,13 +46932,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -47499,10 +46964,10 @@
         <v>85</v>
       </c>
       <c r="M405" t="s" s="2">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="N405" t="s" s="2">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="O405" t="s" s="2">
         <v>391</v>
@@ -47555,7 +47020,7 @@
         <v>75</v>
       </c>
       <c r="AG405" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="AH405" t="s" s="2">
         <v>84</v>
@@ -47572,13 +47037,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="D406" s="2"/>
       <c r="E406" t="s" s="2">
@@ -47604,10 +47069,10 @@
         <v>115</v>
       </c>
       <c r="M406" t="s" s="2">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="N406" t="s" s="2">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="O406" s="2"/>
       <c r="P406" s="2"/>
@@ -47658,7 +47123,7 @@
         <v>75</v>
       </c>
       <c r="AG406" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="AH406" t="s" s="2">
         <v>76</v>
@@ -47667,7 +47132,7 @@
         <v>84</v>
       </c>
       <c r="AJ406" t="s" s="2">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="AK406" t="s" s="2">
         <v>119</v>
@@ -47675,13 +47140,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -47707,13 +47172,13 @@
         <v>234</v>
       </c>
       <c r="M407" t="s" s="2">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="N407" t="s" s="2">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="O407" t="s" s="2">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="P407" s="2"/>
       <c r="Q407" t="s" s="2">
@@ -47763,7 +47228,7 @@
         <v>75</v>
       </c>
       <c r="AG407" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="AH407" t="s" s="2">
         <v>76</v>
@@ -47772,7 +47237,7 @@
         <v>84</v>
       </c>
       <c r="AJ407" t="s" s="2">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="AK407" t="s" s="2">
         <v>75</v>
@@ -47780,13 +47245,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="D408" s="2"/>
       <c r="E408" t="s" s="2">
@@ -47812,13 +47277,13 @@
         <v>75</v>
       </c>
       <c r="M408" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N408" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O408" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P408" s="2"/>
       <c r="Q408" t="s" s="2">
@@ -47868,7 +47333,7 @@
         <v>75</v>
       </c>
       <c r="AG408" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH408" t="s" s="2">
         <v>76</v>
@@ -47885,13 +47350,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D409" t="s" s="2">
         <v>121</v>
@@ -47919,13 +47384,13 @@
         <v>451</v>
       </c>
       <c r="M409" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N409" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O409" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P409" s="2"/>
       <c r="Q409" t="s" s="2">
@@ -47975,7 +47440,7 @@
         <v>75</v>
       </c>
       <c r="AG409" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH409" t="s" s="2">
         <v>76</v>
@@ -47992,13 +47457,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" t="s" s="2">
@@ -48095,13 +47560,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" t="s" s="2">
@@ -48200,13 +47665,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" t="s" s="2">
@@ -48307,13 +47772,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="D413" s="2"/>
       <c r="E413" t="s" s="2">
@@ -48339,10 +47804,10 @@
         <v>85</v>
       </c>
       <c r="M413" t="s" s="2">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="N413" t="s" s="2">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="O413" t="s" s="2">
         <v>391</v>
@@ -48395,7 +47860,7 @@
         <v>75</v>
       </c>
       <c r="AG413" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="AH413" t="s" s="2">
         <v>84</v>
@@ -48412,13 +47877,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" t="s" s="2">
@@ -48444,10 +47909,10 @@
         <v>115</v>
       </c>
       <c r="M414" t="s" s="2">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="N414" t="s" s="2">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="O414" s="2"/>
       <c r="P414" s="2"/>
@@ -48498,7 +47963,7 @@
         <v>75</v>
       </c>
       <c r="AG414" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="AH414" t="s" s="2">
         <v>76</v>
@@ -48507,7 +47972,7 @@
         <v>84</v>
       </c>
       <c r="AJ414" t="s" s="2">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="AK414" t="s" s="2">
         <v>119</v>
@@ -48515,13 +47980,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -48547,13 +48012,13 @@
         <v>234</v>
       </c>
       <c r="M415" t="s" s="2">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="N415" t="s" s="2">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="O415" t="s" s="2">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="P415" s="2"/>
       <c r="Q415" t="s" s="2">
@@ -48603,7 +48068,7 @@
         <v>75</v>
       </c>
       <c r="AG415" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="AH415" t="s" s="2">
         <v>76</v>
@@ -48612,7 +48077,7 @@
         <v>84</v>
       </c>
       <c r="AJ415" t="s" s="2">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="AK415" t="s" s="2">
         <v>75</v>
@@ -48620,13 +48085,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -48652,13 +48117,13 @@
         <v>75</v>
       </c>
       <c r="M416" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N416" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O416" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P416" s="2"/>
       <c r="Q416" t="s" s="2">
@@ -48708,7 +48173,7 @@
         <v>75</v>
       </c>
       <c r="AG416" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH416" t="s" s="2">
         <v>76</v>
@@ -48725,13 +48190,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D417" t="s" s="2">
         <v>130</v>
@@ -48759,13 +48224,13 @@
         <v>451</v>
       </c>
       <c r="M417" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N417" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O417" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P417" s="2"/>
       <c r="Q417" t="s" s="2">
@@ -48815,7 +48280,7 @@
         <v>75</v>
       </c>
       <c r="AG417" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH417" t="s" s="2">
         <v>76</v>
@@ -48832,13 +48297,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -48935,13 +48400,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -49040,13 +48505,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -49147,13 +48612,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" t="s" s="2">
@@ -49179,10 +48644,10 @@
         <v>85</v>
       </c>
       <c r="M421" t="s" s="2">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="N421" t="s" s="2">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="O421" t="s" s="2">
         <v>391</v>
@@ -49235,7 +48700,7 @@
         <v>75</v>
       </c>
       <c r="AG421" t="s" s="2">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="AH421" t="s" s="2">
         <v>84</v>
@@ -49252,13 +48717,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -49284,10 +48749,10 @@
         <v>115</v>
       </c>
       <c r="M422" t="s" s="2">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="N422" t="s" s="2">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="O422" s="2"/>
       <c r="P422" s="2"/>
@@ -49338,7 +48803,7 @@
         <v>75</v>
       </c>
       <c r="AG422" t="s" s="2">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="AH422" t="s" s="2">
         <v>76</v>
@@ -49347,7 +48812,7 @@
         <v>84</v>
       </c>
       <c r="AJ422" t="s" s="2">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="AK422" t="s" s="2">
         <v>119</v>
@@ -49355,13 +48820,13 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" t="s" s="2">
@@ -49387,13 +48852,13 @@
         <v>234</v>
       </c>
       <c r="M423" t="s" s="2">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="N423" t="s" s="2">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="O423" t="s" s="2">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="P423" s="2"/>
       <c r="Q423" t="s" s="2">
@@ -49443,7 +48908,7 @@
         <v>75</v>
       </c>
       <c r="AG423" t="s" s="2">
-        <v>1031</v>
+        <v>1036</v>
       </c>
       <c r="AH423" t="s" s="2">
         <v>76</v>
@@ -49452,7 +48917,7 @@
         <v>84</v>
       </c>
       <c r="AJ423" t="s" s="2">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="AK423" t="s" s="2">
         <v>75</v>
@@ -49460,13 +48925,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" t="s" s="2">
@@ -49492,13 +48957,13 @@
         <v>75</v>
       </c>
       <c r="M424" t="s" s="2">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="N424" t="s" s="2">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="O424" t="s" s="2">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="P424" s="2"/>
       <c r="Q424" t="s" s="2">
@@ -49548,7 +49013,7 @@
         <v>75</v>
       </c>
       <c r="AG424" t="s" s="2">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="AH424" t="s" s="2">
         <v>76</v>
@@ -49561,2847 +49026,6 @@
       </c>
       <c r="AK424" t="s" s="2">
         <v>75</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B425" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="C425" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="D425" s="2"/>
-      <c r="E425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F425" s="2"/>
-      <c r="G425" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H425" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L425" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="M425" t="s" s="2">
-        <v>1095</v>
-      </c>
-      <c r="N425" t="s" s="2">
-        <v>1096</v>
-      </c>
-      <c r="O425" s="2"/>
-      <c r="P425" s="2"/>
-      <c r="Q425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R425" s="2"/>
-      <c r="S425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF425" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG425" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="AH425" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI425" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ425" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK425" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B426" t="s" s="2">
-        <v>1097</v>
-      </c>
-      <c r="C426" t="s" s="2">
-        <v>1097</v>
-      </c>
-      <c r="D426" s="2"/>
-      <c r="E426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F426" s="2"/>
-      <c r="G426" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H426" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L426" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M426" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N426" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="O426" s="2"/>
-      <c r="P426" s="2"/>
-      <c r="Q426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R426" s="2"/>
-      <c r="S426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG426" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH426" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI426" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ426" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK426" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B427" t="s" s="2">
-        <v>1098</v>
-      </c>
-      <c r="C427" t="s" s="2">
-        <v>1098</v>
-      </c>
-      <c r="D427" s="2"/>
-      <c r="E427" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="F427" s="2"/>
-      <c r="G427" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H427" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L427" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="M427" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N427" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O427" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="P427" s="2"/>
-      <c r="Q427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R427" s="2"/>
-      <c r="S427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC427" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD427" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AE427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF427" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG427" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AH427" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI427" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ427" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK427" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B428" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C428" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="D428" s="2"/>
-      <c r="E428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F428" s="2"/>
-      <c r="G428" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H428" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J428" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="K428" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L428" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M428" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N428" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O428" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P428" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="Q428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R428" s="2"/>
-      <c r="S428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y428" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Z428" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AA428" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AB428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG428" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AH428" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI428" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ428" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK428" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B429" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="C429" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="D429" s="2"/>
-      <c r="E429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F429" s="2"/>
-      <c r="G429" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H429" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K429" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L429" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M429" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N429" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O429" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="P429" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Q429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R429" s="2"/>
-      <c r="S429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y429" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Z429" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AA429" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AB429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF429" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG429" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AH429" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI429" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ429" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK429" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B430" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C430" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="D430" s="2"/>
-      <c r="E430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F430" s="2"/>
-      <c r="G430" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H430" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K430" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L430" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M430" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N430" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O430" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="P430" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="Q430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R430" s="2"/>
-      <c r="S430" t="s" s="2">
-        <v>1099</v>
-      </c>
-      <c r="T430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U430" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="V430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG430" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AH430" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI430" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ430" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK430" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B431" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C431" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="D431" s="2"/>
-      <c r="E431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F431" s="2"/>
-      <c r="G431" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H431" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K431" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L431" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M431" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N431" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O431" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="P431" s="2"/>
-      <c r="Q431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R431" s="2"/>
-      <c r="S431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U431" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="V431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG431" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AH431" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI431" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ431" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK431" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B432" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C432" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="D432" s="2"/>
-      <c r="E432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F432" s="2"/>
-      <c r="G432" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H432" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K432" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L432" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M432" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N432" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O432" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="P432" s="2"/>
-      <c r="Q432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R432" s="2"/>
-      <c r="S432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF432" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG432" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AH432" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI432" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ432" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK432" t="s" s="2">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="s" s="2">
-        <v>1087</v>
-      </c>
-      <c r="B433" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C433" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="D433" s="2"/>
-      <c r="E433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F433" s="2"/>
-      <c r="G433" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H433" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K433" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L433" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M433" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N433" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O433" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="P433" s="2"/>
-      <c r="Q433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R433" s="2"/>
-      <c r="S433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF433" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG433" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AH433" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI433" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ433" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK433" t="s" s="2">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B434" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="C434" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="D434" s="2"/>
-      <c r="E434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F434" s="2"/>
-      <c r="G434" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H434" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L434" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="M434" t="s" s="2">
-        <v>1095</v>
-      </c>
-      <c r="N434" t="s" s="2">
-        <v>1096</v>
-      </c>
-      <c r="O434" s="2"/>
-      <c r="P434" s="2"/>
-      <c r="Q434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R434" s="2"/>
-      <c r="S434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF434" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG434" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="AH434" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI434" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ434" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK434" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B435" t="s" s="2">
-        <v>1097</v>
-      </c>
-      <c r="C435" t="s" s="2">
-        <v>1097</v>
-      </c>
-      <c r="D435" s="2"/>
-      <c r="E435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F435" s="2"/>
-      <c r="G435" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H435" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L435" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M435" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N435" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="O435" s="2"/>
-      <c r="P435" s="2"/>
-      <c r="Q435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R435" s="2"/>
-      <c r="S435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG435" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH435" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI435" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ435" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK435" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B436" t="s" s="2">
-        <v>1098</v>
-      </c>
-      <c r="C436" t="s" s="2">
-        <v>1098</v>
-      </c>
-      <c r="D436" s="2"/>
-      <c r="E436" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="F436" s="2"/>
-      <c r="G436" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H436" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L436" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="M436" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N436" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O436" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="P436" s="2"/>
-      <c r="Q436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R436" s="2"/>
-      <c r="S436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC436" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD436" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AE436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF436" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG436" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AH436" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI436" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ436" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK436" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B437" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C437" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="D437" s="2"/>
-      <c r="E437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F437" s="2"/>
-      <c r="G437" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H437" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J437" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="K437" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L437" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M437" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N437" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O437" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P437" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="Q437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R437" s="2"/>
-      <c r="S437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y437" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Z437" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AA437" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AB437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG437" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AH437" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI437" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ437" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK437" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B438" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="C438" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="D438" s="2"/>
-      <c r="E438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F438" s="2"/>
-      <c r="G438" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H438" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K438" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L438" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M438" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N438" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O438" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="P438" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Q438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R438" s="2"/>
-      <c r="S438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y438" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Z438" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AA438" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AB438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF438" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG438" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AH438" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI438" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ438" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK438" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B439" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C439" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="D439" s="2"/>
-      <c r="E439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F439" s="2"/>
-      <c r="G439" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H439" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K439" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L439" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M439" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N439" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O439" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="P439" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="Q439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R439" s="2"/>
-      <c r="S439" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="T439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U439" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="V439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG439" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AH439" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI439" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ439" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK439" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B440" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C440" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="D440" s="2"/>
-      <c r="E440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F440" s="2"/>
-      <c r="G440" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H440" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K440" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L440" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M440" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N440" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O440" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="P440" s="2"/>
-      <c r="Q440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R440" s="2"/>
-      <c r="S440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U440" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="V440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG440" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AH440" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI440" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ440" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK440" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B441" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C441" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="D441" s="2"/>
-      <c r="E441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F441" s="2"/>
-      <c r="G441" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H441" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K441" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L441" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M441" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N441" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O441" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="P441" s="2"/>
-      <c r="Q441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R441" s="2"/>
-      <c r="S441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF441" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG441" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AH441" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI441" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ441" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK441" t="s" s="2">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="s" s="2">
-        <v>1100</v>
-      </c>
-      <c r="B442" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C442" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="D442" s="2"/>
-      <c r="E442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F442" s="2"/>
-      <c r="G442" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H442" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K442" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L442" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M442" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N442" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O442" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="P442" s="2"/>
-      <c r="Q442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R442" s="2"/>
-      <c r="S442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF442" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG442" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AH442" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI442" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ442" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK442" t="s" s="2">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B443" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="C443" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="D443" s="2"/>
-      <c r="E443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F443" s="2"/>
-      <c r="G443" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H443" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L443" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="M443" t="s" s="2">
-        <v>1095</v>
-      </c>
-      <c r="N443" t="s" s="2">
-        <v>1096</v>
-      </c>
-      <c r="O443" s="2"/>
-      <c r="P443" s="2"/>
-      <c r="Q443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R443" s="2"/>
-      <c r="S443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF443" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG443" t="s" s="2">
-        <v>1093</v>
-      </c>
-      <c r="AH443" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI443" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ443" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK443" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B444" t="s" s="2">
-        <v>1097</v>
-      </c>
-      <c r="C444" t="s" s="2">
-        <v>1097</v>
-      </c>
-      <c r="D444" s="2"/>
-      <c r="E444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F444" s="2"/>
-      <c r="G444" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H444" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L444" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M444" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N444" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="O444" s="2"/>
-      <c r="P444" s="2"/>
-      <c r="Q444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R444" s="2"/>
-      <c r="S444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG444" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH444" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI444" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ444" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK444" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B445" t="s" s="2">
-        <v>1098</v>
-      </c>
-      <c r="C445" t="s" s="2">
-        <v>1098</v>
-      </c>
-      <c r="D445" s="2"/>
-      <c r="E445" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="F445" s="2"/>
-      <c r="G445" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H445" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="L445" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="M445" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N445" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O445" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="P445" s="2"/>
-      <c r="Q445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R445" s="2"/>
-      <c r="S445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC445" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD445" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AE445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF445" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG445" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AH445" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI445" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ445" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK445" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B446" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C446" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="D446" s="2"/>
-      <c r="E446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F446" s="2"/>
-      <c r="G446" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H446" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J446" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="K446" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L446" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M446" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N446" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O446" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="P446" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="Q446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R446" s="2"/>
-      <c r="S446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y446" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Z446" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AA446" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AB446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG446" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AH446" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI446" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ446" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK446" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B447" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="C447" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="D447" s="2"/>
-      <c r="E447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F447" s="2"/>
-      <c r="G447" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H447" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K447" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L447" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M447" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N447" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O447" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="P447" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Q447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R447" s="2"/>
-      <c r="S447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y447" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Z447" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AA447" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AB447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF447" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG447" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AH447" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI447" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ447" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK447" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B448" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C448" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="D448" s="2"/>
-      <c r="E448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F448" s="2"/>
-      <c r="G448" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H448" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K448" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L448" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M448" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N448" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O448" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="P448" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="Q448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R448" s="2"/>
-      <c r="S448" t="s" s="2">
-        <v>1110</v>
-      </c>
-      <c r="T448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U448" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="V448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG448" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AH448" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI448" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ448" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK448" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B449" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C449" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="D449" s="2"/>
-      <c r="E449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F449" s="2"/>
-      <c r="G449" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H449" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K449" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L449" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M449" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N449" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O449" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="P449" s="2"/>
-      <c r="Q449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R449" s="2"/>
-      <c r="S449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U449" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="V449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG449" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AH449" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI449" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ449" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK449" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B450" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C450" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="D450" s="2"/>
-      <c r="E450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F450" s="2"/>
-      <c r="G450" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H450" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K450" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L450" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M450" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N450" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O450" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="P450" s="2"/>
-      <c r="Q450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R450" s="2"/>
-      <c r="S450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF450" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG450" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AH450" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI450" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ450" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK450" t="s" s="2">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="B451" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C451" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="D451" s="2"/>
-      <c r="E451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="F451" s="2"/>
-      <c r="G451" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H451" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K451" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L451" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M451" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N451" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O451" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="P451" s="2"/>
-      <c r="Q451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R451" s="2"/>
-      <c r="S451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF451" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG451" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AH451" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI451" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ451" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK451" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
   </sheetData>
